--- a/files/кбжу-example.xlsx
+++ b/files/кбжу-example.xlsx
@@ -11,21 +11,23 @@
     <sheet name="Антропометрия" sheetId="27" r:id="rId2"/>
     <sheet name="КБЖУ" sheetId="13" r:id="rId3"/>
     <sheet name="Продукты" sheetId="1" r:id="rId4"/>
-    <sheet name="Составы" sheetId="3" r:id="rId5"/>
-    <sheet name="Рассчеты" sheetId="2" r:id="rId6"/>
-    <sheet name="Рецепты" sheetId="11" r:id="rId7"/>
-    <sheet name="ПН" sheetId="4" r:id="rId8"/>
-    <sheet name="ВТ" sheetId="21" r:id="rId9"/>
-    <sheet name="СР" sheetId="22" r:id="rId10"/>
-    <sheet name="ЧТ" sheetId="23" r:id="rId11"/>
-    <sheet name="ПТ" sheetId="24" r:id="rId12"/>
-    <sheet name="СБ" sheetId="25" r:id="rId13"/>
-    <sheet name="ВС" sheetId="26" r:id="rId14"/>
+    <sheet name="СухиеПродукты" sheetId="28" r:id="rId5"/>
+    <sheet name="Составы" sheetId="3" r:id="rId6"/>
+    <sheet name="Рассчеты" sheetId="2" r:id="rId7"/>
+    <sheet name="Рецепты" sheetId="11" r:id="rId8"/>
+    <sheet name="ПН" sheetId="4" r:id="rId9"/>
+    <sheet name="ВТ" sheetId="21" r:id="rId10"/>
+    <sheet name="СР" sheetId="22" r:id="rId11"/>
+    <sheet name="ЧТ" sheetId="23" r:id="rId12"/>
+    <sheet name="ПТ" sheetId="24" r:id="rId13"/>
+    <sheet name="СБ" sheetId="25" r:id="rId14"/>
+    <sheet name="ВС" sheetId="26" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName name="БелкиАктивность">"СМЕЩ(Справочник!$H$2;0;0;СЧЁТЕСЛИ(Справочник!$H:$H;""*"")-1;1)"</definedName>
     <definedName name="Пол">OFFSET(Справочник!$C$2,0,0,COUNTIF(Справочник!$C:$C,"*")-1,1)</definedName>
     <definedName name="Продукт">OFFSET(Продукты!$A$2,0,0,COUNTIF(Продукты!$A:$A,"*")-1,1)</definedName>
+    <definedName name="Рецепты" localSheetId="4">OFFSET(СухиеПродукты!#REF!,0,0,COUNTIF(СухиеПродукты!$A:$A,"*")-1,1)</definedName>
     <definedName name="Рецепты">OFFSET(Рецепты!$A$2,0,0,COUNTIF(Рецепты!$A:$A,"*")-1,1)</definedName>
     <definedName name="СписокДат">OFFSET(Антропометрия!$A$2, 0, 0, COUNTA(Антропометрия!$A:$A)-1, 1)</definedName>
     <definedName name="ТДЕАктивность">OFFSET(Справочник!$E$2,0,0,COUNTIF(Справочник!$E:$E,"*")-1,1)</definedName>
@@ -37,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="145">
   <si>
     <t>Белки</t>
   </si>
@@ -409,6 +411,69 @@
   </si>
   <si>
     <t>BMR (с весов, уровень)</t>
+  </si>
+  <si>
+    <t>Вес готового</t>
+  </si>
+  <si>
+    <t>Белки сухого</t>
+  </si>
+  <si>
+    <t>Жиры сухого</t>
+  </si>
+  <si>
+    <t>Углеводы сухого</t>
+  </si>
+  <si>
+    <t>Клетчатка сухого</t>
+  </si>
+  <si>
+    <t>Пищевые волокна сухого</t>
+  </si>
+  <si>
+    <t>Калории сухого</t>
+  </si>
+  <si>
+    <t>Белки готового</t>
+  </si>
+  <si>
+    <t>Жиры готового</t>
+  </si>
+  <si>
+    <t>Углеводы готового</t>
+  </si>
+  <si>
+    <t>Клетчатка готового</t>
+  </si>
+  <si>
+    <t>Пищевые волокна готового</t>
+  </si>
+  <si>
+    <t>Калории готового</t>
+  </si>
+  <si>
+    <t>Желаемый вес готового</t>
+  </si>
+  <si>
+    <t>Нужный вес сухого</t>
+  </si>
+  <si>
+    <t>Коэф (ручной)</t>
+  </si>
+  <si>
+    <t>Коэф (выч.)</t>
+  </si>
+  <si>
+    <t>Вес порции сухой, г</t>
+  </si>
+  <si>
+    <t>Желаемый вес сухого</t>
+  </si>
+  <si>
+    <t>Итоговый вес готового</t>
+  </si>
+  <si>
+    <t>Пищевая ценность, гр</t>
   </si>
 </sst>
 </file>
@@ -420,7 +485,7 @@
     <numFmt numFmtId="165" formatCode="h:mm;@"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -457,6 +522,13 @@
       <color rgb="FF0F1115"/>
       <name val="Segoe UI"/>
       <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
       <charset val="204"/>
     </font>
     <font>
@@ -584,7 +656,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -664,8 +736,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -679,19 +751,19 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
@@ -747,11 +819,23 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="286">
+  <dxfs count="331">
     <dxf>
       <font>
         <b val="0"/>
@@ -2049,7 +2133,7 @@
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="165" formatCode="h:mm;@"/>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -3582,204 +3666,216 @@
         <name val="Times New Roman"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <scheme val="none"/>
-      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -3925,6 +4021,24 @@
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="165" formatCode="h:mm;@"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -3961,6 +4075,24 @@
         <name val="Times New Roman"/>
         <scheme val="none"/>
       </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -3975,24 +4107,6 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
         <color rgb="FF000000"/>
         <name val="Times New Roman"/>
         <scheme val="none"/>
@@ -4011,10 +4125,65 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
         <color rgb="FF000000"/>
         <name val="Times New Roman"/>
         <scheme val="none"/>
       </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -4029,10 +4198,11 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <scheme val="none"/>
-      </font>
+        <color rgb="FF000000"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -4069,25 +4239,804 @@
         <name val="Times New Roman"/>
         <scheme val="none"/>
       </font>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
       <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <scheme val="none"/>
-      </font>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -4102,29 +5051,29 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
         <color rgb="FF000000"/>
         <name val="Times New Roman"/>
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <scheme val="none"/>
-      </font>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -4139,10 +5088,397 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
         <color rgb="FF000000"/>
         <name val="Times New Roman"/>
         <scheme val="none"/>
       </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
       <numFmt numFmtId="164" formatCode="0.000"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -4180,6 +5516,117 @@
         <name val="Times New Roman"/>
         <scheme val="none"/>
       </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
       <numFmt numFmtId="164" formatCode="0.000"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -4328,529 +5775,8 @@
         <name val="Times New Roman"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <name val="Times New Roman"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <name val="Times New Roman"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="1" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -5684,7 +6610,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="Антропометрия" displayName="Антропометрия" ref="A1:AE2" totalsRowShown="0" headerRowDxfId="285" dataDxfId="284">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="Антропометрия" displayName="Антропометрия" ref="A1:AE2" totalsRowShown="0" headerRowDxfId="330" dataDxfId="329">
   <autoFilter ref="A1:AE2">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -5719,61 +6645,61 @@
     <filterColumn colId="30" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="31">
-    <tableColumn id="1" name="Дата" dataDxfId="283"/>
-    <tableColumn id="2" name="Вес, кг" dataDxfId="282"/>
-    <tableColumn id="3" name="Рост, см" dataDxfId="281"/>
-    <tableColumn id="4" name="Возраст, лет" dataDxfId="280"/>
-    <tableColumn id="5" name="Пол" dataDxfId="279"/>
-    <tableColumn id="6" name="Шея, см" dataDxfId="278"/>
-    <tableColumn id="7" name="Грудь, см" dataDxfId="277"/>
-    <tableColumn id="8" name="Плечи, см" dataDxfId="276"/>
-    <tableColumn id="9" name="Рука правая, см" dataDxfId="275"/>
-    <tableColumn id="10" name="Рука левая, см" dataDxfId="274"/>
-    <tableColumn id="11" name="Талия, см" dataDxfId="273"/>
-    <tableColumn id="12" name="Бедра, см" dataDxfId="272"/>
-    <tableColumn id="13" name="Бедро левое, см" dataDxfId="271"/>
-    <tableColumn id="14" name="Бедро правое, см" dataDxfId="270"/>
-    <tableColumn id="15" name="Икра правая, см" dataDxfId="269"/>
-    <tableColumn id="16" name="Икра левая, см" dataDxfId="268"/>
+    <tableColumn id="1" name="Дата" dataDxfId="328"/>
+    <tableColumn id="2" name="Вес, кг" dataDxfId="327"/>
+    <tableColumn id="3" name="Рост, см" dataDxfId="326"/>
+    <tableColumn id="4" name="Возраст, лет" dataDxfId="325"/>
+    <tableColumn id="5" name="Пол" dataDxfId="324"/>
+    <tableColumn id="6" name="Шея, см" dataDxfId="323"/>
+    <tableColumn id="7" name="Грудь, см" dataDxfId="322"/>
+    <tableColumn id="8" name="Плечи, см" dataDxfId="321"/>
+    <tableColumn id="9" name="Рука правая, см" dataDxfId="320"/>
+    <tableColumn id="10" name="Рука левая, см" dataDxfId="319"/>
+    <tableColumn id="11" name="Талия, см" dataDxfId="318"/>
+    <tableColumn id="12" name="Бедра, см" dataDxfId="317"/>
+    <tableColumn id="13" name="Бедро левое, см" dataDxfId="316"/>
+    <tableColumn id="14" name="Бедро правое, см" dataDxfId="315"/>
+    <tableColumn id="15" name="Икра правая, см" dataDxfId="314"/>
+    <tableColumn id="16" name="Икра левая, см" dataDxfId="313"/>
     <tableColumn id="23" name="% жира (весы)"/>
-    <tableColumn id="17" name="% жира, Формула Navy" dataDxfId="267">
+    <tableColumn id="17" name="% жира, Формула Navy" dataDxfId="312">
       <calculatedColumnFormula>MIN(MAX(IF(Антропометрия[Пол]=Справочник!$C$2,86.01*LOG10(Антропометрия[Талия, см] - Антропометрия[Шея, см]) - 70.041*LOG10(Антропометрия[Рост, см]) + 36.76,163.205*LOG10(Антропометрия[Талия, см] + Антропометрия[Бедра, см] - Антропометрия[Шея, см]) - 97.684*LOG10(Антропометрия[Рост, см]) - 78.387), 5), 50)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="25" name="Уровень % жира" dataDxfId="266">
+    <tableColumn id="25" name="Уровень % жира" dataDxfId="311">
       <calculatedColumnFormula>IFERROR(VLOOKUP(IF(Антропометрия[% жира (весы)]&lt;&gt;"",Антропометрия[% жира (весы)],Антропометрия[% жира, Формула Navy]), Справочник!$T$3:$V$6,3,TRUE), "Вне диапазона")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" name="Мышечная масса, кг" dataDxfId="265">
+    <tableColumn id="18" name="Мышечная масса, кг" dataDxfId="310">
       <calculatedColumnFormula>Антропометрия[Вес, кг]*(100-Антропометрия[% жира, Формула Navy])/100</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="26" name="Уровень мышечной массы" dataDxfId="264">
+    <tableColumn id="26" name="Уровень мышечной массы" dataDxfId="309">
       <calculatedColumnFormula>VLOOKUP(Антропометрия[Мышечная масса, кг], Справочник!$X$3:$Z$5, 3, TRUE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" name="Висцеральный жир (рассчет)" dataDxfId="263">
+    <tableColumn id="19" name="Висцеральный жир (рассчет)" dataDxfId="308">
       <calculatedColumnFormula>MIN(20, MAX(0, ( Антропометрия[Талия, см] / Антропометрия[Рост, см] - 0.4 ) * 50 ))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="27" name="Висцеральный жир (уровень)" dataDxfId="262">
+    <tableColumn id="27" name="Висцеральный жир (уровень)" dataDxfId="307">
       <calculatedColumnFormula>VLOOKUP(Антропометрия[Висцеральный жир (рассчет)], Справочник!$AB$3:$AD$5, 3, TRUE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" name="Костная масса, кг (рассчет)" dataDxfId="261">
+    <tableColumn id="20" name="Костная масса, кг (рассчет)" dataDxfId="306">
       <calculatedColumnFormula>IF(Антропометрия[Пол]=Справочник!$C$2, Антропометрия[Вес, кг] * 0.04, Антропометрия[Вес, кг] * 0.03)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="28" name="Костная масса, кг, уровень" dataDxfId="260">
+    <tableColumn id="28" name="Костная масса, кг, уровень" dataDxfId="305">
       <calculatedColumnFormula>VLOOKUP(Антропометрия[Костная масса, кг (рассчет)], Справочник!$AF$3:$AH$5, 3, TRUE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" name="ИМТ (расчёт)" dataDxfId="259">
+    <tableColumn id="21" name="ИМТ (расчёт)" dataDxfId="304">
       <calculatedColumnFormula>Антропометрия[[#This Row],[Вес, кг]]/((Антропометрия[[#This Row],[Рост, см]]/100)^2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="29" name="ИМТ (уровень)" dataDxfId="258">
+    <tableColumn id="29" name="ИМТ (уровень)" dataDxfId="303">
       <calculatedColumnFormula>VLOOKUP(Антропометрия[ИМТ (расчёт)], Справочник!$AJ$3:$AL$5, 3, TRUE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" name="BMR (расчёт)" dataDxfId="257">
+    <tableColumn id="22" name="BMR (расчёт)" dataDxfId="302">
       <calculatedColumnFormula>10*Антропометрия[[#This Row],[Вес, кг]]+6.25*Антропометрия[[#This Row],[Рост, см]]-5*Антропометрия[[#This Row],[Возраст, лет]]+IF(Антропометрия[[#This Row],[Пол]]=Справочник!$C$2,5,-161)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="30" name="BMR (уровень)" dataDxfId="256">
+    <tableColumn id="30" name="BMR (уровень)" dataDxfId="301">
       <calculatedColumnFormula>VLOOKUP(Антропометрия[BMR (расчёт)], Справочник!$AN$3:$AP$5, 3, TRUE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="24" name="BMR (с весов)" dataDxfId="255"/>
-    <tableColumn id="31" name="BMR (с весов, уровень)" dataDxfId="254">
+    <tableColumn id="24" name="BMR (с весов)" dataDxfId="300"/>
+    <tableColumn id="31" name="BMR (с весов, уровень)" dataDxfId="299">
       <calculatedColumnFormula>IF(Антропометрия[BMR (с весов)]&lt;&gt;"",VLOOKUP(Антропометрия[BMR (с весов)], Справочник!$AN$3:$AP$5, 3, TRUE),"")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5782,6 +6708,61 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="ЧТ" displayName="ЧТ" ref="A1:L2" headerRowDxfId="103" dataDxfId="102">
+  <autoFilter ref="A1:L2">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+    <filterColumn colId="3" hiddenButton="1"/>
+    <filterColumn colId="4" hiddenButton="1"/>
+    <filterColumn colId="5" hiddenButton="1"/>
+    <filterColumn colId="6" hiddenButton="1"/>
+    <filterColumn colId="7" hiddenButton="1"/>
+    <filterColumn colId="8" hiddenButton="1"/>
+    <filterColumn colId="9" hiddenButton="1"/>
+    <filterColumn colId="10" hiddenButton="1"/>
+    <filterColumn colId="11" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="12">
+    <tableColumn id="11" name="Тип питания" dataDxfId="101" totalsRowDxfId="100"/>
+    <tableColumn id="1" name="Продукт" totalsRowLabel="Итог" dataDxfId="99" totalsRowDxfId="98"/>
+    <tableColumn id="12" name="Время приёма" dataDxfId="97" totalsRowDxfId="96"/>
+    <tableColumn id="9" name="Вес" totalsRowFunction="custom" dataDxfId="95" totalsRowDxfId="94">
+      <totalsRowFormula>SUMPRODUCT(ЧТ[Вес], ЧТ[Количество])</totalsRowFormula>
+    </tableColumn>
+    <tableColumn id="10" name="Количество" totalsRowFunction="sum" dataDxfId="93" totalsRowDxfId="92"/>
+    <tableColumn id="2" name="Исх. Вес." totalsRowFunction="sum" dataDxfId="91" totalsRowDxfId="90">
+      <calculatedColumnFormula>INDEX(Продукты!$H:$H, MATCH(ЧТ[[#This Row],[Продукт]], Продукты!$A:$A, 0))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="3" name="Белки" totalsRowFunction="custom" dataDxfId="89" totalsRowDxfId="88">
+      <calculatedColumnFormula>INDEX(Продукты!$B:$B, MATCH(ЧТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ЧТ[[#This Row],[Вес]]/ЧТ[Исх. Вес.])*ЧТ[Количество]</calculatedColumnFormula>
+      <totalsRowFormula>SUMPRODUCT(ЧТ[Белки], ЧТ[Количество])</totalsRowFormula>
+    </tableColumn>
+    <tableColumn id="4" name="Жиры" totalsRowFunction="custom" dataDxfId="87" totalsRowDxfId="86">
+      <calculatedColumnFormula>INDEX(Продукты!$C:$C, MATCH(ЧТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ЧТ[[#This Row],[Вес]]/ЧТ[Исх. Вес.])*ЧТ[Количество]</calculatedColumnFormula>
+      <totalsRowFormula>SUMPRODUCT(ЧТ[Жиры], ЧТ[Количество])</totalsRowFormula>
+    </tableColumn>
+    <tableColumn id="5" name="Углеводы" totalsRowFunction="custom" dataDxfId="85" totalsRowDxfId="84">
+      <calculatedColumnFormula>INDEX(Продукты!$D:$D, MATCH(ЧТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ЧТ[[#This Row],[Вес]]/ЧТ[Исх. Вес.])*ЧТ[Количество]</calculatedColumnFormula>
+      <totalsRowFormula>SUMPRODUCT(ЧТ[Углеводы], ЧТ[Количество])</totalsRowFormula>
+    </tableColumn>
+    <tableColumn id="6" name="Клетчатка" totalsRowFunction="custom" dataDxfId="83" totalsRowDxfId="82">
+      <calculatedColumnFormula>INDEX(Продукты!$E:$E, MATCH(ЧТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ЧТ[[#This Row],[Вес]]/ЧТ[Исх. Вес.])*ЧТ[Количество]</calculatedColumnFormula>
+      <totalsRowFormula>SUMPRODUCT(ЧТ[Клетчатка], ЧТ[Количество])</totalsRowFormula>
+    </tableColumn>
+    <tableColumn id="7" name="Пищевые волокна" totalsRowFunction="custom" dataDxfId="81" totalsRowDxfId="80">
+      <calculatedColumnFormula>INDEX(Продукты!$F:$F, MATCH(ЧТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ЧТ[[#This Row],[Вес]]/ЧТ[Исх. Вес.])*ЧТ[Количество]</calculatedColumnFormula>
+      <totalsRowFormula>SUMPRODUCT(ЧТ[Пищевые волокна], ЧТ[Количество])</totalsRowFormula>
+    </tableColumn>
+    <tableColumn id="8" name="Калории, ккл" totalsRowFunction="sum" dataDxfId="79" totalsRowDxfId="78">
+      <calculatedColumnFormula>INDEX(Продукты!$G:$G, MATCH(ЧТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ЧТ[[#This Row],[Вес]]/ЧТ[Исх. Вес.])*ЧТ[Количество]</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="ПТ" displayName="ПТ" ref="A1:L2" headerRowDxfId="77" dataDxfId="76">
   <autoFilter ref="A1:L2">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -5809,34 +6790,34 @@
       <calculatedColumnFormula>INDEX(Продукты!$H:$H, MATCH(ПТ[[#This Row],[Продукт]], Продукты!$A:$A, 0))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="3" name="Белки" totalsRowFunction="custom" dataDxfId="63" totalsRowDxfId="62">
-      <calculatedColumnFormula>INDEX(Продукты!$B:$B, MATCH(ПТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ПТ[[#This Row],[Вес]]/100)*ПТ[Количество]</calculatedColumnFormula>
+      <calculatedColumnFormula>INDEX(Продукты!$B:$B, MATCH(ПТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ПТ[[#This Row],[Вес]]/ПТ[Исх. Вес.])*ПТ[Количество]</calculatedColumnFormula>
       <totalsRowFormula>SUMPRODUCT(ПТ[Белки], ПТ[Количество])</totalsRowFormula>
     </tableColumn>
     <tableColumn id="4" name="Жиры" totalsRowFunction="custom" dataDxfId="61" totalsRowDxfId="60">
-      <calculatedColumnFormula>INDEX(Продукты!$C:$C, MATCH(ПТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ПТ[[#This Row],[Вес]]/100)*ПТ[Количество]</calculatedColumnFormula>
+      <calculatedColumnFormula>INDEX(Продукты!$C:$C, MATCH(ПТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ПТ[[#This Row],[Вес]]/ПТ[Исх. Вес.])*ПТ[Количество]</calculatedColumnFormula>
       <totalsRowFormula>SUMPRODUCT(ПТ[Жиры], ПТ[Количество])</totalsRowFormula>
     </tableColumn>
     <tableColumn id="5" name="Углеводы" totalsRowFunction="custom" dataDxfId="59" totalsRowDxfId="58">
-      <calculatedColumnFormula>INDEX(Продукты!$D:$D, MATCH(ПТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ПТ[[#This Row],[Вес]]/100)*ПТ[Количество]</calculatedColumnFormula>
+      <calculatedColumnFormula>INDEX(Продукты!$D:$D, MATCH(ПТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ПТ[[#This Row],[Вес]]/ПТ[Исх. Вес.])*ПТ[Количество]</calculatedColumnFormula>
       <totalsRowFormula>SUMPRODUCT(ПТ[Углеводы], ПТ[Количество])</totalsRowFormula>
     </tableColumn>
     <tableColumn id="6" name="Клетчатка" totalsRowFunction="custom" dataDxfId="57" totalsRowDxfId="56">
-      <calculatedColumnFormula>INDEX(Продукты!$E:$E, MATCH(ПТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ПТ[[#This Row],[Вес]]/100)*ПТ[Количество]</calculatedColumnFormula>
+      <calculatedColumnFormula>INDEX(Продукты!$E:$E, MATCH(ПТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ПТ[[#This Row],[Вес]]/ПТ[Исх. Вес.])*ПТ[Количество]</calculatedColumnFormula>
       <totalsRowFormula>SUMPRODUCT(ПТ[Клетчатка], ПТ[Количество])</totalsRowFormula>
     </tableColumn>
     <tableColumn id="7" name="Пищевые волокна" totalsRowFunction="custom" dataDxfId="55" totalsRowDxfId="54">
-      <calculatedColumnFormula>INDEX(Продукты!$F:$F, MATCH(ПТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ПТ[[#This Row],[Вес]]/100)*ПТ[Количество]</calculatedColumnFormula>
+      <calculatedColumnFormula>INDEX(Продукты!$F:$F, MATCH(ПТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ПТ[[#This Row],[Вес]]/ПТ[Исх. Вес.])*ПТ[Количество]</calculatedColumnFormula>
       <totalsRowFormula>SUMPRODUCT(ПТ[Пищевые волокна], ПТ[Количество])</totalsRowFormula>
     </tableColumn>
     <tableColumn id="8" name="Калории, ккл" totalsRowFunction="sum" dataDxfId="53" totalsRowDxfId="52">
-      <calculatedColumnFormula>INDEX(Продукты!$G:$G, MATCH(ПТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ПТ[[#This Row],[Вес]]/100)*ПТ[Количество]</calculatedColumnFormula>
+      <calculatedColumnFormula>INDEX(Продукты!$G:$G, MATCH(ПТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ПТ[[#This Row],[Вес]]/ПТ[Исх. Вес.])*ПТ[Количество]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
-<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="СБ" displayName="СБ" ref="A1:L2" headerRowDxfId="51" dataDxfId="50">
   <autoFilter ref="A1:L2">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -5864,34 +6845,34 @@
       <calculatedColumnFormula>INDEX(Продукты!$H:$H, MATCH(СБ[[#This Row],[Продукт]], Продукты!$A:$A, 0))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="3" name="Белки" totalsRowFunction="custom" dataDxfId="37" totalsRowDxfId="36">
-      <calculatedColumnFormula>INDEX(Продукты!$B:$B, MATCH(СБ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (СБ[[#This Row],[Вес]]/100)*СБ[Количество]</calculatedColumnFormula>
+      <calculatedColumnFormula>INDEX(Продукты!$B:$B, MATCH(СБ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (СБ[[#This Row],[Вес]]/СБ[Исх. Вес.])*СБ[Количество]</calculatedColumnFormula>
       <totalsRowFormula>SUMPRODUCT(СБ[Белки], СБ[Количество])</totalsRowFormula>
     </tableColumn>
     <tableColumn id="4" name="Жиры" totalsRowFunction="custom" dataDxfId="35" totalsRowDxfId="34">
-      <calculatedColumnFormula>INDEX(Продукты!$C:$C, MATCH(СБ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (СБ[[#This Row],[Вес]]/100)*СБ[Количество]</calculatedColumnFormula>
+      <calculatedColumnFormula>INDEX(Продукты!$C:$C, MATCH(СБ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (СБ[[#This Row],[Вес]]/СБ[Исх. Вес.])*СБ[Количество]</calculatedColumnFormula>
       <totalsRowFormula>SUMPRODUCT(СБ[Жиры], СБ[Количество])</totalsRowFormula>
     </tableColumn>
     <tableColumn id="5" name="Углеводы" totalsRowFunction="custom" dataDxfId="33" totalsRowDxfId="32">
-      <calculatedColumnFormula>INDEX(Продукты!$D:$D, MATCH(СБ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (СБ[[#This Row],[Вес]]/100)*СБ[Количество]</calculatedColumnFormula>
+      <calculatedColumnFormula>INDEX(Продукты!$D:$D, MATCH(СБ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (СБ[[#This Row],[Вес]]/СБ[Исх. Вес.])*СБ[Количество]</calculatedColumnFormula>
       <totalsRowFormula>SUMPRODUCT(СБ[Углеводы], СБ[Количество])</totalsRowFormula>
     </tableColumn>
     <tableColumn id="6" name="Клетчатка" totalsRowFunction="custom" dataDxfId="31" totalsRowDxfId="30">
-      <calculatedColumnFormula>INDEX(Продукты!$E:$E, MATCH(СБ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (СБ[[#This Row],[Вес]]/100)*СБ[Количество]</calculatedColumnFormula>
+      <calculatedColumnFormula>INDEX(Продукты!$E:$E, MATCH(СБ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (СБ[[#This Row],[Вес]]/СБ[Исх. Вес.])*СБ[Количество]</calculatedColumnFormula>
       <totalsRowFormula>SUMPRODUCT(СБ[Клетчатка], СБ[Количество])</totalsRowFormula>
     </tableColumn>
     <tableColumn id="7" name="Пищевые волокна" totalsRowFunction="custom" dataDxfId="29" totalsRowDxfId="28">
-      <calculatedColumnFormula>INDEX(Продукты!$F:$F, MATCH(СБ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (СБ[[#This Row],[Вес]]/100)*СБ[Количество]</calculatedColumnFormula>
+      <calculatedColumnFormula>INDEX(Продукты!$F:$F, MATCH(СБ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (СБ[[#This Row],[Вес]]/СБ[Исх. Вес.])*СБ[Количество]</calculatedColumnFormula>
       <totalsRowFormula>SUMPRODUCT(СБ[Пищевые волокна], СБ[Количество])</totalsRowFormula>
     </tableColumn>
     <tableColumn id="8" name="Калории, ккл" totalsRowFunction="sum" dataDxfId="27" totalsRowDxfId="26">
-      <calculatedColumnFormula>INDEX(Продукты!$G:$G, MATCH(СБ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (СБ[[#This Row],[Вес]]/100)*СБ[Количество]</calculatedColumnFormula>
+      <calculatedColumnFormula>INDEX(Продукты!$G:$G, MATCH(СБ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (СБ[[#This Row],[Вес]]/СБ[Исх. Вес.])*СБ[Количество]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
-<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="ВС" displayName="ВС" ref="A1:L2" headerRowDxfId="25" dataDxfId="24">
   <autoFilter ref="A1:L2">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -5919,27 +6900,27 @@
       <calculatedColumnFormula>INDEX(Продукты!$H:$H, MATCH(ВС[[#This Row],[Продукт]], Продукты!$A:$A, 0))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="3" name="Белки" totalsRowFunction="custom" dataDxfId="11" totalsRowDxfId="10">
-      <calculatedColumnFormula>INDEX(Продукты!$B:$B, MATCH(ВС[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ВС[[#This Row],[Вес]]/100)*ВС[Количество]</calculatedColumnFormula>
+      <calculatedColumnFormula>INDEX(Продукты!$B:$B, MATCH(ВС[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ВС[[#This Row],[Вес]]/ВС[Исх. Вес.])*ВС[Количество]</calculatedColumnFormula>
       <totalsRowFormula>SUMPRODUCT(ВС[Белки], ВС[Количество])</totalsRowFormula>
     </tableColumn>
     <tableColumn id="4" name="Жиры" totalsRowFunction="custom" dataDxfId="9" totalsRowDxfId="8">
-      <calculatedColumnFormula>INDEX(Продукты!$C:$C, MATCH(ВС[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ВС[[#This Row],[Вес]]/100)*ВС[Количество]</calculatedColumnFormula>
+      <calculatedColumnFormula>INDEX(Продукты!$C:$C, MATCH(ВС[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ВС[[#This Row],[Вес]]/ВС[Исх. Вес.])*ВС[Количество]</calculatedColumnFormula>
       <totalsRowFormula>SUMPRODUCT(ВС[Жиры], ВС[Количество])</totalsRowFormula>
     </tableColumn>
     <tableColumn id="5" name="Углеводы" totalsRowFunction="custom" dataDxfId="7" totalsRowDxfId="6">
-      <calculatedColumnFormula>INDEX(Продукты!$D:$D, MATCH(ВС[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ВС[[#This Row],[Вес]]/100)*ВС[Количество]</calculatedColumnFormula>
+      <calculatedColumnFormula>INDEX(Продукты!$D:$D, MATCH(ВС[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ВС[[#This Row],[Вес]]/ВС[Исх. Вес.])*ВС[Количество]</calculatedColumnFormula>
       <totalsRowFormula>SUMPRODUCT(ВС[Углеводы], ВС[Количество])</totalsRowFormula>
     </tableColumn>
     <tableColumn id="6" name="Клетчатка" totalsRowFunction="custom" dataDxfId="5" totalsRowDxfId="4">
-      <calculatedColumnFormula>INDEX(Продукты!$E:$E, MATCH(ВС[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ВС[[#This Row],[Вес]]/100)*ВС[Количество]</calculatedColumnFormula>
+      <calculatedColumnFormula>INDEX(Продукты!$E:$E, MATCH(ВС[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ВС[[#This Row],[Вес]]/ВС[Исх. Вес.])*ВС[Количество]</calculatedColumnFormula>
       <totalsRowFormula>SUMPRODUCT(ВС[Клетчатка], ВС[Количество])</totalsRowFormula>
     </tableColumn>
     <tableColumn id="7" name="Пищевые волокна" totalsRowFunction="custom" dataDxfId="3" totalsRowDxfId="2">
-      <calculatedColumnFormula>INDEX(Продукты!$F:$F, MATCH(ВС[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ВС[[#This Row],[Вес]]/100)*ВС[Количество]</calculatedColumnFormula>
+      <calculatedColumnFormula>INDEX(Продукты!$F:$F, MATCH(ВС[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ВС[[#This Row],[Вес]]/ВС[Исх. Вес.])*ВС[Количество]</calculatedColumnFormula>
       <totalsRowFormula>SUMPRODUCT(ВС[Пищевые волокна], ВС[Количество])</totalsRowFormula>
     </tableColumn>
     <tableColumn id="8" name="Калории, ккл" totalsRowFunction="sum" dataDxfId="1" totalsRowDxfId="0">
-      <calculatedColumnFormula>INDEX(Продукты!$G:$G, MATCH(ВС[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ВС[[#This Row],[Вес]]/100)*ВС[Количество]</calculatedColumnFormula>
+      <calculatedColumnFormula>INDEX(Продукты!$G:$G, MATCH(ВС[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ВС[[#This Row],[Вес]]/ВС[Исх. Вес.])*ВС[Количество]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -5975,58 +6956,58 @@
     <filterColumn colId="23" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="24">
-    <tableColumn id="20" name="Дата" dataDxfId="253"/>
-    <tableColumn id="1" name="Вес" dataDxfId="252"/>
-    <tableColumn id="2" name="Рост" dataDxfId="251"/>
-    <tableColumn id="3" name="Возраст" dataDxfId="250"/>
-    <tableColumn id="4" name="Пол" dataDxfId="249"/>
-    <tableColumn id="5" name="Активность" dataDxfId="248"/>
-    <tableColumn id="6" name="Цель" dataDxfId="247"/>
-    <tableColumn id="17" name="TDEE коэфф." dataDxfId="246">
+    <tableColumn id="20" name="Дата" dataDxfId="298"/>
+    <tableColumn id="1" name="Вес" dataDxfId="297"/>
+    <tableColumn id="2" name="Рост" dataDxfId="296"/>
+    <tableColumn id="3" name="Возраст" dataDxfId="295"/>
+    <tableColumn id="4" name="Пол" dataDxfId="294"/>
+    <tableColumn id="5" name="Активность" dataDxfId="293"/>
+    <tableColumn id="6" name="Цель" dataDxfId="292"/>
+    <tableColumn id="17" name="TDEE коэфф." dataDxfId="291">
       <calculatedColumnFormula>VLOOKUP(Таблица4[[#This Row],[Активность]], Справочник!$E$2:$F$7, 2, 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="23" name="Коэф белки низ" dataDxfId="245">
+    <tableColumn id="23" name="Коэф белки низ" dataDxfId="290">
       <calculatedColumnFormula>VLOOKUP(Таблица4[[#This Row],[Активность]], Справочник!$H$2:$J$7, 2, 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" name="Коэф белки верх" dataDxfId="244">
+    <tableColumn id="22" name="Коэф белки верх" dataDxfId="289">
       <calculatedColumnFormula>VLOOKUP(Таблица4[[#This Row],[Активность]], Справочник!$H$2:$J$7, 3, 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" name="Коэф.Жир низ" dataDxfId="243"/>
-    <tableColumn id="18" name="Коэф. Жир верх" dataDxfId="242"/>
-    <tableColumn id="25" name="Кэф дифицита низ" dataDxfId="241">
+    <tableColumn id="19" name="Коэф.Жир низ" dataDxfId="288"/>
+    <tableColumn id="18" name="Коэф. Жир верх" dataDxfId="287"/>
+    <tableColumn id="25" name="Кэф дифицита низ" dataDxfId="286">
       <calculatedColumnFormula>VLOOKUP(Таблица4[[#This Row],[Цель]], Справочник!$P$2:$R$5, 2, 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="24" name="Коэф дифицита верх" dataDxfId="240">
+    <tableColumn id="24" name="Коэф дифицита верх" dataDxfId="285">
       <calculatedColumnFormula>VLOOKUP(Таблица4[[#This Row],[Цель]], Справочник!$P$2:$R$5, 3, 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" name="BMR" dataDxfId="239">
+    <tableColumn id="7" name="BMR" dataDxfId="284">
       <calculatedColumnFormula>10*Таблица4[Вес]+6.25*Таблица4[Рост]-5*Таблица4[Возраст]+IF(Таблица4[[#This Row],[Пол]]=Справочник!$C$2,5,-161)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" name="TDEE" dataDxfId="238">
+    <tableColumn id="8" name="TDEE" dataDxfId="283">
       <calculatedColumnFormula>Таблица4[BMR]*Таблица4[TDEE коэфф.]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" name="Белки низ" dataDxfId="237">
+    <tableColumn id="11" name="Белки низ" dataDxfId="282">
       <calculatedColumnFormula>Таблица4[Вес]*Таблица4[Коэф белки низ]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" name="Белки верх" dataDxfId="236">
+    <tableColumn id="12" name="Белки верх" dataDxfId="281">
       <calculatedColumnFormula>Таблица4[Вес]*Таблица4[Коэф белки верх]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" name="Жиры низ" dataDxfId="235">
+    <tableColumn id="13" name="Жиры низ" dataDxfId="280">
       <calculatedColumnFormula>Таблица4[Вес]*Таблица4[Коэф.Жир низ]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" name="Жиры верх" dataDxfId="234">
+    <tableColumn id="14" name="Жиры верх" dataDxfId="279">
       <calculatedColumnFormula>Таблица4[Вес]*Таблица4[Коэф. Жир верх]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" name="Углеводы низ" dataDxfId="233">
+    <tableColumn id="15" name="Углеводы низ" dataDxfId="278">
       <calculatedColumnFormula>(Таблица4[Калории мин]-(Таблица4[Белки верх]*4+Таблица4[Жиры верх]*9))/4</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" name="Углеводы верх" dataDxfId="232">
+    <tableColumn id="16" name="Углеводы верх" dataDxfId="277">
       <calculatedColumnFormula>(Таблица4[Калории макс]-(Таблица4[Белки низ]*4+Таблица4[Жиры низ]*9))/4</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" name="Калории мин" dataDxfId="231">
+    <tableColumn id="9" name="Калории мин" dataDxfId="276">
       <calculatedColumnFormula>Таблица4[TDEE]-Таблица4[Коэф дифицита верх]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" name="Калории макс" dataDxfId="230">
+    <tableColumn id="10" name="Калории макс" dataDxfId="275">
       <calculatedColumnFormula>Таблица4[TDEE]-Таблица4[Кэф дифицита низ]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6035,6 +7016,78 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="СухиеПродукты" displayName="СухиеПродукты" ref="A1:V2" headerRowDxfId="274" dataDxfId="273">
+  <autoFilter ref="A1:V2">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+    <filterColumn colId="3" hiddenButton="1"/>
+    <filterColumn colId="4" hiddenButton="1"/>
+    <filterColumn colId="5" hiddenButton="1"/>
+    <filterColumn colId="6" hiddenButton="1"/>
+    <filterColumn colId="7" hiddenButton="1"/>
+    <filterColumn colId="8" hiddenButton="1"/>
+    <filterColumn colId="9" hiddenButton="1"/>
+    <filterColumn colId="10" hiddenButton="1"/>
+    <filterColumn colId="11" hiddenButton="1"/>
+    <filterColumn colId="12" hiddenButton="1"/>
+    <filterColumn colId="13" hiddenButton="1"/>
+    <filterColumn colId="14" hiddenButton="1"/>
+    <filterColumn colId="15" hiddenButton="1"/>
+    <filterColumn colId="16" hiddenButton="1"/>
+    <filterColumn colId="17" hiddenButton="1"/>
+    <filterColumn colId="18" hiddenButton="1"/>
+    <filterColumn colId="19" hiddenButton="1"/>
+    <filterColumn colId="20" hiddenButton="1"/>
+    <filterColumn colId="21" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="22">
+    <tableColumn id="1" name="Название" totalsRowLabel="Итог" dataDxfId="272"/>
+    <tableColumn id="4" name="Белки сухого" dataDxfId="271" totalsRowDxfId="270"/>
+    <tableColumn id="5" name="Жиры сухого" dataDxfId="269" totalsRowDxfId="268"/>
+    <tableColumn id="6" name="Углеводы сухого" dataDxfId="267" totalsRowDxfId="266"/>
+    <tableColumn id="7" name="Клетчатка сухого" dataDxfId="265" totalsRowDxfId="264"/>
+    <tableColumn id="8" name="Пищевые волокна сухого" dataDxfId="263" totalsRowDxfId="262"/>
+    <tableColumn id="9" name="Калории сухого" dataDxfId="261" totalsRowDxfId="260"/>
+    <tableColumn id="10" name="Пищевая ценность, гр" dataDxfId="259" totalsRowDxfId="258"/>
+    <tableColumn id="20" name="Вес порции сухой, г" dataDxfId="257" totalsRowDxfId="256"/>
+    <tableColumn id="2" name="Вес готового" dataDxfId="255" totalsRowDxfId="254"/>
+    <tableColumn id="3" name="Коэф (выч.)" dataDxfId="253" totalsRowDxfId="252">
+      <calculatedColumnFormula>IF(AND(СухиеПродукты[Вес готового]&lt;&gt;"",СухиеПродукты[Вес готового]&lt;&gt;""),СухиеПродукты[Вес готового]/СухиеПродукты[Вес порции сухой, г],0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="19" name="Коэф (ручной)" dataDxfId="251" totalsRowDxfId="250"/>
+    <tableColumn id="11" name="Белки готового" dataDxfId="249" totalsRowDxfId="248">
+      <calculatedColumnFormula>IF(СухиеПродукты[Коэф (выч.)]&lt;&gt;0,СухиеПродукты[Белки сухого]/СухиеПродукты[Коэф (выч.)],СухиеПродукты[Белки сухого]/СухиеПродукты[Коэф (ручной)])</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="12" name="Жиры готового" dataDxfId="247" totalsRowDxfId="246">
+      <calculatedColumnFormula>IF(СухиеПродукты[Коэф (выч.)]&lt;&gt;0,СухиеПродукты[Жиры сухого]/СухиеПродукты[Коэф (выч.)],СухиеПродукты[Жиры сухого]/СухиеПродукты[Коэф (ручной)])</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="13" name="Углеводы готового" dataDxfId="245" totalsRowDxfId="244">
+      <calculatedColumnFormula>IF(СухиеПродукты[Коэф (выч.)]&lt;&gt;0,СухиеПродукты[Углеводы сухого]/СухиеПродукты[Коэф (выч.)],СухиеПродукты[Углеводы сухого]/СухиеПродукты[Коэф (ручной)])</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="14" name="Клетчатка готового" dataDxfId="243" totalsRowDxfId="242">
+      <calculatedColumnFormula>IF(СухиеПродукты[Коэф (выч.)]&lt;&gt;0,СухиеПродукты[Клетчатка сухого]/СухиеПродукты[Коэф (выч.)],СухиеПродукты[Клетчатка сухого]/СухиеПродукты[Коэф (ручной)])</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="15" name="Пищевые волокна готового" dataDxfId="241" totalsRowDxfId="240">
+      <calculatedColumnFormula>IF(СухиеПродукты[Коэф (выч.)]&lt;&gt;0,СухиеПродукты[Пищевые волокна сухого]/СухиеПродукты[Коэф (выч.)],СухиеПродукты[Пищевые волокна сухого]/СухиеПродукты[Коэф (ручной)])</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="16" name="Калории готового" dataDxfId="239" totalsRowDxfId="238">
+      <calculatedColumnFormula>IF(СухиеПродукты[Коэф (выч.)]&lt;&gt;0,СухиеПродукты[Калории сухого]/СухиеПродукты[Коэф (выч.)],СухиеПродукты[Калории сухого]/СухиеПродукты[Коэф (ручной)])</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="17" name="Желаемый вес готового" dataDxfId="237" totalsRowDxfId="236"/>
+    <tableColumn id="18" name="Нужный вес сухого" dataDxfId="235" totalsRowDxfId="234">
+      <calculatedColumnFormula>IF(СухиеПродукты[Коэф (выч.)]&lt;&gt;0,СухиеПродукты[Желаемый вес готового]/СухиеПродукты[Коэф (выч.)],СухиеПродукты[Желаемый вес готового]/СухиеПродукты[Коэф (ручной)])</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="21" name="Желаемый вес сухого" dataDxfId="233" totalsRowDxfId="232"/>
+    <tableColumn id="22" name="Итоговый вес готового" dataDxfId="231" totalsRowDxfId="230">
+      <calculatedColumnFormula>IF(СухиеПродукты[Коэф (выч.)]&lt;&gt;0,СухиеПродукты[Желаемый вес сухого]*СухиеПродукты[Коэф (выч.)],СухиеПродукты[Желаемый вес сухого]*СухиеПродукты[Коэф (ручной)])</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Состав" displayName="Состав" ref="A1:B3" headerRowDxfId="229" dataDxfId="228">
   <autoFilter ref="A1:B3">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -6048,7 +7101,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Рассчет" displayName="Рассчет" ref="A1:J2" headerRowDxfId="223" dataDxfId="222">
   <autoFilter ref="A1:J2">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -6064,42 +7117,40 @@
   </autoFilter>
   <tableColumns count="10">
     <tableColumn id="1" name="Продукт" totalsRowLabel="Итог" dataDxfId="221" totalsRowDxfId="220"/>
-    <tableColumn id="9" name="Вес, гр" totalsRowFunction="custom" dataDxfId="219" totalsRowDxfId="218">
-      <totalsRowFormula>SUMPRODUCT(Рассчет[Вес, гр], Рассчет[Количество])</totalsRowFormula>
-    </tableColumn>
+    <tableColumn id="9" name="Вес, гр" totalsRowFunction="sum" dataDxfId="219" totalsRowDxfId="218"/>
     <tableColumn id="10" name="Количество" totalsRowFunction="sum" dataDxfId="217" totalsRowDxfId="216"/>
     <tableColumn id="2" name="Исх. Вес. гр" totalsRowFunction="sum" dataDxfId="215" totalsRowDxfId="214">
       <calculatedColumnFormula>INDEX(Продукты!$H:$H, MATCH(Рассчет[[#This Row],[Продукт]], Продукты!$A:$A, 0))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="3" name="Белки" totalsRowFunction="custom" dataDxfId="213" totalsRowDxfId="212">
-      <calculatedColumnFormula>INDEX(Продукты!$B:$B, MATCH(Рассчет[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (Рассчет[[#This Row],[Вес, гр]]/100)*Рассчет[Количество]</calculatedColumnFormula>
+      <calculatedColumnFormula>INDEX(Продукты!$B:$B, MATCH(Рассчет[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (Рассчет[[#This Row],[Вес, гр]]/Рассчет[Исх. Вес. гр])*Рассчет[Количество]</calculatedColumnFormula>
       <totalsRowFormula>SUMPRODUCT(Рассчет[Белки], Рассчет[Количество])</totalsRowFormula>
     </tableColumn>
     <tableColumn id="4" name="Жиры" totalsRowFunction="custom" dataDxfId="211" totalsRowDxfId="210">
-      <calculatedColumnFormula>INDEX(Продукты!$C:$C, MATCH(Рассчет[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (Рассчет[[#This Row],[Вес, гр]]/100)*Рассчет[Количество]</calculatedColumnFormula>
+      <calculatedColumnFormula>INDEX(Продукты!$C:$C, MATCH(Рассчет[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (Рассчет[[#This Row],[Вес, гр]]/Рассчет[Исх. Вес. гр])*Рассчет[Количество]</calculatedColumnFormula>
       <totalsRowFormula>SUMPRODUCT(Рассчет[Жиры], Рассчет[Количество])</totalsRowFormula>
     </tableColumn>
     <tableColumn id="5" name="Углеводы" totalsRowFunction="custom" dataDxfId="209" totalsRowDxfId="208">
-      <calculatedColumnFormula>INDEX(Продукты!$D:$D, MATCH(Рассчет[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (Рассчет[[#This Row],[Вес, гр]]/100)*Рассчет[Количество]</calculatedColumnFormula>
+      <calculatedColumnFormula>INDEX(Продукты!$D:$D, MATCH(Рассчет[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (Рассчет[[#This Row],[Вес, гр]]/Рассчет[Исх. Вес. гр])*Рассчет[Количество]</calculatedColumnFormula>
       <totalsRowFormula>SUMPRODUCT(Рассчет[Углеводы], Рассчет[Количество])</totalsRowFormula>
     </tableColumn>
     <tableColumn id="6" name="Клетчатка" totalsRowFunction="custom" dataDxfId="207" totalsRowDxfId="206">
-      <calculatedColumnFormula>INDEX(Продукты!$E:$E, MATCH(Рассчет[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (Рассчет[[#This Row],[Вес, гр]]/100)*Рассчет[Количество]</calculatedColumnFormula>
+      <calculatedColumnFormula>INDEX(Продукты!$E:$E, MATCH(Рассчет[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (Рассчет[[#This Row],[Вес, гр]]/Рассчет[Исх. Вес. гр])*Рассчет[Количество]</calculatedColumnFormula>
       <totalsRowFormula>SUMPRODUCT(Рассчет[Клетчатка], Рассчет[Количество])</totalsRowFormula>
     </tableColumn>
     <tableColumn id="7" name="Пищевые волокна" totalsRowFunction="custom" dataDxfId="205" totalsRowDxfId="204">
-      <calculatedColumnFormula>INDEX(Продукты!$F:$F, MATCH(Рассчет[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (Рассчет[[#This Row],[Вес, гр]]/100)*Рассчет[Количество]</calculatedColumnFormula>
+      <calculatedColumnFormula>INDEX(Продукты!$F:$F, MATCH(Рассчет[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (Рассчет[[#This Row],[Вес, гр]]/Рассчет[Исх. Вес. гр])*Рассчет[Количество]</calculatedColumnFormula>
       <totalsRowFormula>SUMPRODUCT(Рассчет[Пищевые волокна], Рассчет[Количество])</totalsRowFormula>
     </tableColumn>
     <tableColumn id="8" name="Калории, ккл" totalsRowFunction="sum" dataDxfId="203" totalsRowDxfId="202">
-      <calculatedColumnFormula>INDEX(Продукты!$G:$G, MATCH(Рассчет[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (Рассчет[[#This Row],[Вес, гр]]/100)*Рассчет[Количество]</calculatedColumnFormula>
+      <calculatedColumnFormula>INDEX(Продукты!$G:$G, MATCH(Рассчет[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (Рассчет[[#This Row],[Вес, гр]]/Рассчет[Исх. Вес. гр])*Рассчет[Количество]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
-<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="Рецепт" displayName="Рецепт" ref="A1:I3" headerRowDxfId="201" dataDxfId="200">
   <autoFilter ref="A1:I3">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -6127,7 +7178,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="ПН" displayName="ПН" ref="A1:L2" headerRowDxfId="181" dataDxfId="180">
   <autoFilter ref="A1:L2">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -6155,34 +7206,34 @@
       <calculatedColumnFormula>INDEX(Продукты!$H:$H, MATCH(ПН[[#This Row],[Продукт]], Продукты!$A:$A, 0))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="3" name="Белки" totalsRowFunction="custom" dataDxfId="167" totalsRowDxfId="166">
-      <calculatedColumnFormula>INDEX(Продукты!$B:$B, MATCH(ПН[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ПН[[#This Row],[Вес]]/100)*ПН[Количество]</calculatedColumnFormula>
+      <calculatedColumnFormula>INDEX(Продукты!$B:$B, MATCH(ПН[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ПН[[#This Row],[Вес]]/ПН[Исх. Вес.])*ПН[Количество]</calculatedColumnFormula>
       <totalsRowFormula>SUMPRODUCT(ПН[Белки], ПН[Количество])</totalsRowFormula>
     </tableColumn>
     <tableColumn id="4" name="Жиры" totalsRowFunction="custom" dataDxfId="165" totalsRowDxfId="164">
-      <calculatedColumnFormula>INDEX(Продукты!$C:$C, MATCH(ПН[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ПН[[#This Row],[Вес]]/100)*ПН[Количество]</calculatedColumnFormula>
+      <calculatedColumnFormula>INDEX(Продукты!$C:$C, MATCH(ПН[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ПН[[#This Row],[Вес]]/ПН[Исх. Вес.])*ПН[Количество]</calculatedColumnFormula>
       <totalsRowFormula>SUMPRODUCT(ПН[Жиры], ПН[Количество])</totalsRowFormula>
     </tableColumn>
     <tableColumn id="5" name="Углеводы" totalsRowFunction="custom" dataDxfId="163" totalsRowDxfId="162">
-      <calculatedColumnFormula>INDEX(Продукты!$D:$D, MATCH(ПН[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ПН[[#This Row],[Вес]]/100)*ПН[Количество]</calculatedColumnFormula>
+      <calculatedColumnFormula>INDEX(Продукты!$D:$D, MATCH(ПН[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ПН[[#This Row],[Вес]]/ПН[Исх. Вес.])*ПН[Количество]</calculatedColumnFormula>
       <totalsRowFormula>SUMPRODUCT(ПН[Углеводы], ПН[Количество])</totalsRowFormula>
     </tableColumn>
     <tableColumn id="6" name="Клетчатка" totalsRowFunction="custom" dataDxfId="161" totalsRowDxfId="160">
-      <calculatedColumnFormula>INDEX(Продукты!$E:$E, MATCH(ПН[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ПН[[#This Row],[Вес]]/100)*ПН[Количество]</calculatedColumnFormula>
+      <calculatedColumnFormula>INDEX(Продукты!$E:$E, MATCH(ПН[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ПН[[#This Row],[Вес]]/ПН[Исх. Вес.])*ПН[Количество]</calculatedColumnFormula>
       <totalsRowFormula>SUMPRODUCT(ПН[Клетчатка], ПН[Количество])</totalsRowFormula>
     </tableColumn>
     <tableColumn id="7" name="Пищевые волокна" totalsRowFunction="custom" dataDxfId="159" totalsRowDxfId="158">
-      <calculatedColumnFormula>INDEX(Продукты!$F:$F, MATCH(ПН[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ПН[[#This Row],[Вес]]/100)*ПН[Количество]</calculatedColumnFormula>
+      <calculatedColumnFormula>INDEX(Продукты!$F:$F, MATCH(ПН[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ПН[[#This Row],[Вес]]/ПН[Исх. Вес.])*ПН[Количество]</calculatedColumnFormula>
       <totalsRowFormula>SUMPRODUCT(ПН[Пищевые волокна], ПН[Количество])</totalsRowFormula>
     </tableColumn>
     <tableColumn id="8" name="Калории, ккл" totalsRowFunction="sum" dataDxfId="157" totalsRowDxfId="156">
-      <calculatedColumnFormula>INDEX(Продукты!$G:$G, MATCH(ПН[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ПН[[#This Row],[Вес]]/100)*ПН[Количество]</calculatedColumnFormula>
+      <calculatedColumnFormula>INDEX(Продукты!$G:$G, MATCH(ПН[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ПН[[#This Row],[Вес]]/ПН[Исх. Вес.])*ПН[Количество]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
-<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="ВТ" displayName="ВТ" ref="A1:L2" headerRowDxfId="155" dataDxfId="154">
   <autoFilter ref="A1:L2">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -6210,34 +7261,34 @@
       <calculatedColumnFormula>INDEX(Продукты!$H:$H, MATCH(ВТ[[#This Row],[Продукт]], Продукты!$A:$A, 0))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="3" name="Белки" totalsRowFunction="custom" dataDxfId="141" totalsRowDxfId="140">
-      <calculatedColumnFormula>INDEX(Продукты!$B:$B, MATCH(ВТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ВТ[[#This Row],[Вес]]/100)*ВТ[Количество]</calculatedColumnFormula>
+      <calculatedColumnFormula>INDEX(Продукты!$B:$B, MATCH(ВТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ВТ[[#This Row],[Вес]]/ВТ[Исх. Вес.])*ВТ[Количество]</calculatedColumnFormula>
       <totalsRowFormula>SUMPRODUCT(ВТ[Белки], ВТ[Количество])</totalsRowFormula>
     </tableColumn>
     <tableColumn id="4" name="Жиры" totalsRowFunction="custom" dataDxfId="139" totalsRowDxfId="138">
-      <calculatedColumnFormula>INDEX(Продукты!$C:$C, MATCH(ВТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ВТ[[#This Row],[Вес]]/100)*ВТ[Количество]</calculatedColumnFormula>
+      <calculatedColumnFormula>INDEX(Продукты!$C:$C, MATCH(ВТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ВТ[[#This Row],[Вес]]/ВТ[Исх. Вес.])*ВТ[Количество]</calculatedColumnFormula>
       <totalsRowFormula>SUMPRODUCT(ВТ[Жиры], ВТ[Количество])</totalsRowFormula>
     </tableColumn>
     <tableColumn id="5" name="Углеводы" totalsRowFunction="custom" dataDxfId="137" totalsRowDxfId="136">
-      <calculatedColumnFormula>INDEX(Продукты!$D:$D, MATCH(ВТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ВТ[[#This Row],[Вес]]/100)*ВТ[Количество]</calculatedColumnFormula>
+      <calculatedColumnFormula>INDEX(Продукты!$D:$D, MATCH(ВТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ВТ[[#This Row],[Вес]]/ВТ[Исх. Вес.])*ВТ[Количество]</calculatedColumnFormula>
       <totalsRowFormula>SUMPRODUCT(ВТ[Углеводы], ВТ[Количество])</totalsRowFormula>
     </tableColumn>
     <tableColumn id="6" name="Клетчатка" totalsRowFunction="custom" dataDxfId="135" totalsRowDxfId="134">
-      <calculatedColumnFormula>INDEX(Продукты!$E:$E, MATCH(ВТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ВТ[[#This Row],[Вес]]/100)*ВТ[Количество]</calculatedColumnFormula>
+      <calculatedColumnFormula>INDEX(Продукты!$E:$E, MATCH(ВТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ВТ[[#This Row],[Вес]]/ВТ[Исх. Вес.])*ВТ[Количество]</calculatedColumnFormula>
       <totalsRowFormula>SUMPRODUCT(ВТ[Клетчатка], ВТ[Количество])</totalsRowFormula>
     </tableColumn>
     <tableColumn id="7" name="Пищевые волокна" totalsRowFunction="custom" dataDxfId="133" totalsRowDxfId="132">
-      <calculatedColumnFormula>INDEX(Продукты!$F:$F, MATCH(ВТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ВТ[[#This Row],[Вес]]/100)*ВТ[Количество]</calculatedColumnFormula>
+      <calculatedColumnFormula>INDEX(Продукты!$F:$F, MATCH(ВТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ВТ[[#This Row],[Вес]]/ВТ[Исх. Вес.])*ВТ[Количество]</calculatedColumnFormula>
       <totalsRowFormula>SUMPRODUCT(ВТ[Пищевые волокна], ВТ[Количество])</totalsRowFormula>
     </tableColumn>
     <tableColumn id="8" name="Калории, ккл" totalsRowFunction="sum" dataDxfId="131" totalsRowDxfId="130">
-      <calculatedColumnFormula>INDEX(Продукты!$G:$G, MATCH(ВТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ВТ[[#This Row],[Вес]]/100)*ВТ[Количество]</calculatedColumnFormula>
+      <calculatedColumnFormula>INDEX(Продукты!$G:$G, MATCH(ВТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ВТ[[#This Row],[Вес]]/ВТ[Исх. Вес.])*ВТ[Количество]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
-<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="СР" displayName="СР" ref="A1:L2" headerRowDxfId="129" dataDxfId="128">
   <autoFilter ref="A1:L2">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -6265,82 +7316,27 @@
       <calculatedColumnFormula>INDEX(Продукты!$H:$H, MATCH(СР[[#This Row],[Продукт]], Продукты!$A:$A, 0))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="3" name="Белки" totalsRowFunction="custom" dataDxfId="115" totalsRowDxfId="114">
-      <calculatedColumnFormula>INDEX(Продукты!$B:$B, MATCH(СР[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (СР[[#This Row],[Вес]]/100)*СР[Количество]</calculatedColumnFormula>
+      <calculatedColumnFormula>INDEX(Продукты!$B:$B, MATCH(СР[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (СР[[#This Row],[Вес]]/СР[Исх. Вес.])*СР[Количество]</calculatedColumnFormula>
       <totalsRowFormula>SUMPRODUCT(СР[Белки], СР[Количество])</totalsRowFormula>
     </tableColumn>
     <tableColumn id="4" name="Жиры" totalsRowFunction="custom" dataDxfId="113" totalsRowDxfId="112">
-      <calculatedColumnFormula>INDEX(Продукты!$C:$C, MATCH(СР[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (СР[[#This Row],[Вес]]/100)*СР[Количество]</calculatedColumnFormula>
+      <calculatedColumnFormula>INDEX(Продукты!$C:$C, MATCH(СР[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (СР[[#This Row],[Вес]]/СР[Исх. Вес.])*СР[Количество]</calculatedColumnFormula>
       <totalsRowFormula>SUMPRODUCT(СР[Жиры], СР[Количество])</totalsRowFormula>
     </tableColumn>
     <tableColumn id="5" name="Углеводы" totalsRowFunction="custom" dataDxfId="111" totalsRowDxfId="110">
-      <calculatedColumnFormula>INDEX(Продукты!$D:$D, MATCH(СР[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (СР[[#This Row],[Вес]]/100)*СР[Количество]</calculatedColumnFormula>
+      <calculatedColumnFormula>INDEX(Продукты!$D:$D, MATCH(СР[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (СР[[#This Row],[Вес]]/СР[Исх. Вес.])*СР[Количество]</calculatedColumnFormula>
       <totalsRowFormula>SUMPRODUCT(СР[Углеводы], СР[Количество])</totalsRowFormula>
     </tableColumn>
     <tableColumn id="6" name="Клетчатка" totalsRowFunction="custom" dataDxfId="109" totalsRowDxfId="108">
-      <calculatedColumnFormula>INDEX(Продукты!$E:$E, MATCH(СР[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (СР[[#This Row],[Вес]]/100)*СР[Количество]</calculatedColumnFormula>
+      <calculatedColumnFormula>INDEX(Продукты!$E:$E, MATCH(СР[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (СР[[#This Row],[Вес]]/СР[Исх. Вес.])*СР[Количество]</calculatedColumnFormula>
       <totalsRowFormula>SUMPRODUCT(СР[Клетчатка], СР[Количество])</totalsRowFormula>
     </tableColumn>
     <tableColumn id="7" name="Пищевые волокна" totalsRowFunction="custom" dataDxfId="107" totalsRowDxfId="106">
-      <calculatedColumnFormula>INDEX(Продукты!$F:$F, MATCH(СР[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (СР[[#This Row],[Вес]]/100)*СР[Количество]</calculatedColumnFormula>
+      <calculatedColumnFormula>INDEX(Продукты!$F:$F, MATCH(СР[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (СР[[#This Row],[Вес]]/СР[Исх. Вес.])*СР[Количество]</calculatedColumnFormula>
       <totalsRowFormula>SUMPRODUCT(СР[Пищевые волокна], СР[Количество])</totalsRowFormula>
     </tableColumn>
     <tableColumn id="8" name="Калории, ккл" totalsRowFunction="sum" dataDxfId="105" totalsRowDxfId="104">
-      <calculatedColumnFormula>INDEX(Продукты!$G:$G, MATCH(СР[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (СР[[#This Row],[Вес]]/100)*СР[Количество]</calculatedColumnFormula>
-    </tableColumn>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="ЧТ" displayName="ЧТ" ref="A1:L2" headerRowDxfId="103" dataDxfId="102">
-  <autoFilter ref="A1:L2">
-    <filterColumn colId="0" hiddenButton="1"/>
-    <filterColumn colId="1" hiddenButton="1"/>
-    <filterColumn colId="2" hiddenButton="1"/>
-    <filterColumn colId="3" hiddenButton="1"/>
-    <filterColumn colId="4" hiddenButton="1"/>
-    <filterColumn colId="5" hiddenButton="1"/>
-    <filterColumn colId="6" hiddenButton="1"/>
-    <filterColumn colId="7" hiddenButton="1"/>
-    <filterColumn colId="8" hiddenButton="1"/>
-    <filterColumn colId="9" hiddenButton="1"/>
-    <filterColumn colId="10" hiddenButton="1"/>
-    <filterColumn colId="11" hiddenButton="1"/>
-  </autoFilter>
-  <tableColumns count="12">
-    <tableColumn id="11" name="Тип питания" dataDxfId="101" totalsRowDxfId="100"/>
-    <tableColumn id="1" name="Продукт" totalsRowLabel="Итог" dataDxfId="99" totalsRowDxfId="98"/>
-    <tableColumn id="12" name="Время приёма" dataDxfId="97" totalsRowDxfId="96"/>
-    <tableColumn id="9" name="Вес" totalsRowFunction="custom" dataDxfId="95" totalsRowDxfId="94">
-      <totalsRowFormula>SUMPRODUCT(ЧТ[Вес], ЧТ[Количество])</totalsRowFormula>
-    </tableColumn>
-    <tableColumn id="10" name="Количество" totalsRowFunction="sum" dataDxfId="93" totalsRowDxfId="92"/>
-    <tableColumn id="2" name="Исх. Вес." totalsRowFunction="sum" dataDxfId="91" totalsRowDxfId="90">
-      <calculatedColumnFormula>INDEX(Продукты!$H:$H, MATCH(ЧТ[[#This Row],[Продукт]], Продукты!$A:$A, 0))</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="3" name="Белки" totalsRowFunction="custom" dataDxfId="89" totalsRowDxfId="88">
-      <calculatedColumnFormula>INDEX(Продукты!$B:$B, MATCH(ЧТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ЧТ[[#This Row],[Вес]]/100)*ЧТ[Количество]</calculatedColumnFormula>
-      <totalsRowFormula>SUMPRODUCT(ЧТ[Белки], ЧТ[Количество])</totalsRowFormula>
-    </tableColumn>
-    <tableColumn id="4" name="Жиры" totalsRowFunction="custom" dataDxfId="87" totalsRowDxfId="86">
-      <calculatedColumnFormula>INDEX(Продукты!$C:$C, MATCH(ЧТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ЧТ[[#This Row],[Вес]]/100)*ЧТ[Количество]</calculatedColumnFormula>
-      <totalsRowFormula>SUMPRODUCT(ЧТ[Жиры], ЧТ[Количество])</totalsRowFormula>
-    </tableColumn>
-    <tableColumn id="5" name="Углеводы" totalsRowFunction="custom" dataDxfId="85" totalsRowDxfId="84">
-      <calculatedColumnFormula>INDEX(Продукты!$D:$D, MATCH(ЧТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ЧТ[[#This Row],[Вес]]/100)*ЧТ[Количество]</calculatedColumnFormula>
-      <totalsRowFormula>SUMPRODUCT(ЧТ[Углеводы], ЧТ[Количество])</totalsRowFormula>
-    </tableColumn>
-    <tableColumn id="6" name="Клетчатка" totalsRowFunction="custom" dataDxfId="83" totalsRowDxfId="82">
-      <calculatedColumnFormula>INDEX(Продукты!$E:$E, MATCH(ЧТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ЧТ[[#This Row],[Вес]]/100)*ЧТ[Количество]</calculatedColumnFormula>
-      <totalsRowFormula>SUMPRODUCT(ЧТ[Клетчатка], ЧТ[Количество])</totalsRowFormula>
-    </tableColumn>
-    <tableColumn id="7" name="Пищевые волокна" totalsRowFunction="custom" dataDxfId="81" totalsRowDxfId="80">
-      <calculatedColumnFormula>INDEX(Продукты!$F:$F, MATCH(ЧТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ЧТ[[#This Row],[Вес]]/100)*ЧТ[Количество]</calculatedColumnFormula>
-      <totalsRowFormula>SUMPRODUCT(ЧТ[Пищевые волокна], ЧТ[Количество])</totalsRowFormula>
-    </tableColumn>
-    <tableColumn id="8" name="Калории, ккл" totalsRowFunction="sum" dataDxfId="79" totalsRowDxfId="78">
-      <calculatedColumnFormula>INDEX(Продукты!$G:$G, MATCH(ЧТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ЧТ[[#This Row],[Вес]]/100)*ЧТ[Количество]</calculatedColumnFormula>
+      <calculatedColumnFormula>INDEX(Продукты!$G:$G, MATCH(СР[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (СР[[#This Row],[Вес]]/СР[Исх. Вес.])*СР[Количество]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -7055,10 +8051,10 @@
         <v>63</v>
       </c>
       <c r="Q5" s="49">
+        <v>-500</v>
+      </c>
+      <c r="R5" s="48">
         <v>-300</v>
-      </c>
-      <c r="R5" s="48">
-        <v>-500</v>
       </c>
       <c r="T5" s="34">
         <v>20</v>
@@ -7229,41 +8225,41 @@
       <c r="B2" s="2"/>
       <c r="C2" s="13"/>
       <c r="F2" s="1" t="e">
-        <f>INDEX(Продукты!$H:$H, MATCH(СР[[#This Row],[Продукт]], Продукты!$A:$A, 0))</f>
+        <f>INDEX(Продукты!$H:$H, MATCH(ВТ[[#This Row],[Продукт]], Продукты!$A:$A, 0))</f>
         <v>#N/A</v>
       </c>
       <c r="G2" s="1" t="e">
-        <f>INDEX(Продукты!$B:$B, MATCH(СР[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (СР[[#This Row],[Вес]]/100)*СР[Количество]</f>
+        <f>INDEX(Продукты!$B:$B, MATCH(ВТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ВТ[[#This Row],[Вес]]/ВТ[Исх. Вес.])*ВТ[Количество]</f>
         <v>#N/A</v>
       </c>
       <c r="H2" s="1" t="e">
-        <f>INDEX(Продукты!$C:$C, MATCH(СР[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (СР[[#This Row],[Вес]]/100)*СР[Количество]</f>
+        <f>INDEX(Продукты!$C:$C, MATCH(ВТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ВТ[[#This Row],[Вес]]/ВТ[Исх. Вес.])*ВТ[Количество]</f>
         <v>#N/A</v>
       </c>
       <c r="I2" s="1" t="e">
-        <f>INDEX(Продукты!$D:$D, MATCH(СР[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (СР[[#This Row],[Вес]]/100)*СР[Количество]</f>
+        <f>INDEX(Продукты!$D:$D, MATCH(ВТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ВТ[[#This Row],[Вес]]/ВТ[Исх. Вес.])*ВТ[Количество]</f>
         <v>#N/A</v>
       </c>
       <c r="J2" s="1" t="e">
-        <f>INDEX(Продукты!$E:$E, MATCH(СР[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (СР[[#This Row],[Вес]]/100)*СР[Количество]</f>
+        <f>INDEX(Продукты!$E:$E, MATCH(ВТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ВТ[[#This Row],[Вес]]/ВТ[Исх. Вес.])*ВТ[Количество]</f>
         <v>#N/A</v>
       </c>
       <c r="K2" s="1" t="e">
-        <f>INDEX(Продукты!$F:$F, MATCH(СР[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (СР[[#This Row],[Вес]]/100)*СР[Количество]</f>
+        <f>INDEX(Продукты!$F:$F, MATCH(ВТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ВТ[[#This Row],[Вес]]/ВТ[Исх. Вес.])*ВТ[Количество]</f>
         <v>#N/A</v>
       </c>
       <c r="L2" s="1" t="e">
-        <f>INDEX(Продукты!$G:$G, MATCH(СР[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (СР[[#This Row],[Вес]]/100)*СР[Количество]</f>
+        <f>INDEX(Продукты!$G:$G, MATCH(ВТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ВТ[[#This Row],[Вес]]/ВТ[Исх. Вес.])*ВТ[Количество]</f>
         <v>#N/A</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2">
+      <formula1>ТипПитания</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2">
       <formula1>Продукт</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2">
-      <formula1>ТипПитания</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7336,41 +8332,41 @@
       <c r="B2" s="2"/>
       <c r="C2" s="13"/>
       <c r="F2" s="1" t="e">
-        <f>INDEX(Продукты!$H:$H, MATCH(ЧТ[[#This Row],[Продукт]], Продукты!$A:$A, 0))</f>
+        <f>INDEX(Продукты!$H:$H, MATCH(СР[[#This Row],[Продукт]], Продукты!$A:$A, 0))</f>
         <v>#N/A</v>
       </c>
       <c r="G2" s="1" t="e">
-        <f>INDEX(Продукты!$B:$B, MATCH(ЧТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ЧТ[[#This Row],[Вес]]/100)*ЧТ[Количество]</f>
+        <f>INDEX(Продукты!$B:$B, MATCH(СР[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (СР[[#This Row],[Вес]]/СР[Исх. Вес.])*СР[Количество]</f>
         <v>#N/A</v>
       </c>
       <c r="H2" s="1" t="e">
-        <f>INDEX(Продукты!$C:$C, MATCH(ЧТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ЧТ[[#This Row],[Вес]]/100)*ЧТ[Количество]</f>
+        <f>INDEX(Продукты!$C:$C, MATCH(СР[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (СР[[#This Row],[Вес]]/СР[Исх. Вес.])*СР[Количество]</f>
         <v>#N/A</v>
       </c>
       <c r="I2" s="1" t="e">
-        <f>INDEX(Продукты!$D:$D, MATCH(ЧТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ЧТ[[#This Row],[Вес]]/100)*ЧТ[Количество]</f>
+        <f>INDEX(Продукты!$D:$D, MATCH(СР[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (СР[[#This Row],[Вес]]/СР[Исх. Вес.])*СР[Количество]</f>
         <v>#N/A</v>
       </c>
       <c r="J2" s="1" t="e">
-        <f>INDEX(Продукты!$E:$E, MATCH(ЧТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ЧТ[[#This Row],[Вес]]/100)*ЧТ[Количество]</f>
+        <f>INDEX(Продукты!$E:$E, MATCH(СР[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (СР[[#This Row],[Вес]]/СР[Исх. Вес.])*СР[Количество]</f>
         <v>#N/A</v>
       </c>
       <c r="K2" s="1" t="e">
-        <f>INDEX(Продукты!$F:$F, MATCH(ЧТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ЧТ[[#This Row],[Вес]]/100)*ЧТ[Количество]</f>
+        <f>INDEX(Продукты!$F:$F, MATCH(СР[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (СР[[#This Row],[Вес]]/СР[Исх. Вес.])*СР[Количество]</f>
         <v>#N/A</v>
       </c>
       <c r="L2" s="1" t="e">
-        <f>INDEX(Продукты!$G:$G, MATCH(ЧТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ЧТ[[#This Row],[Вес]]/100)*ЧТ[Количество]</f>
+        <f>INDEX(Продукты!$G:$G, MATCH(СР[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (СР[[#This Row],[Вес]]/СР[Исх. Вес.])*СР[Количество]</f>
         <v>#N/A</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2">
+      <formula1>Продукт</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2">
       <formula1>ТипПитания</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2">
-      <formula1>Продукт</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7443,41 +8439,41 @@
       <c r="B2" s="2"/>
       <c r="C2" s="13"/>
       <c r="F2" s="1" t="e">
-        <f>INDEX(Продукты!$H:$H, MATCH(ПТ[[#This Row],[Продукт]], Продукты!$A:$A, 0))</f>
+        <f>INDEX(Продукты!$H:$H, MATCH(ЧТ[[#This Row],[Продукт]], Продукты!$A:$A, 0))</f>
         <v>#N/A</v>
       </c>
       <c r="G2" s="1" t="e">
-        <f>INDEX(Продукты!$B:$B, MATCH(ПТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ПТ[[#This Row],[Вес]]/100)*ПТ[Количество]</f>
+        <f>INDEX(Продукты!$B:$B, MATCH(ЧТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ЧТ[[#This Row],[Вес]]/ЧТ[Исх. Вес.])*ЧТ[Количество]</f>
         <v>#N/A</v>
       </c>
       <c r="H2" s="1" t="e">
-        <f>INDEX(Продукты!$C:$C, MATCH(ПТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ПТ[[#This Row],[Вес]]/100)*ПТ[Количество]</f>
+        <f>INDEX(Продукты!$C:$C, MATCH(ЧТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ЧТ[[#This Row],[Вес]]/ЧТ[Исх. Вес.])*ЧТ[Количество]</f>
         <v>#N/A</v>
       </c>
       <c r="I2" s="1" t="e">
-        <f>INDEX(Продукты!$D:$D, MATCH(ПТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ПТ[[#This Row],[Вес]]/100)*ПТ[Количество]</f>
+        <f>INDEX(Продукты!$D:$D, MATCH(ЧТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ЧТ[[#This Row],[Вес]]/ЧТ[Исх. Вес.])*ЧТ[Количество]</f>
         <v>#N/A</v>
       </c>
       <c r="J2" s="1" t="e">
-        <f>INDEX(Продукты!$E:$E, MATCH(ПТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ПТ[[#This Row],[Вес]]/100)*ПТ[Количество]</f>
+        <f>INDEX(Продукты!$E:$E, MATCH(ЧТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ЧТ[[#This Row],[Вес]]/ЧТ[Исх. Вес.])*ЧТ[Количество]</f>
         <v>#N/A</v>
       </c>
       <c r="K2" s="1" t="e">
-        <f>INDEX(Продукты!$F:$F, MATCH(ПТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ПТ[[#This Row],[Вес]]/100)*ПТ[Количество]</f>
+        <f>INDEX(Продукты!$F:$F, MATCH(ЧТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ЧТ[[#This Row],[Вес]]/ЧТ[Исх. Вес.])*ЧТ[Количество]</f>
         <v>#N/A</v>
       </c>
       <c r="L2" s="1" t="e">
-        <f>INDEX(Продукты!$G:$G, MATCH(ПТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ПТ[[#This Row],[Вес]]/100)*ПТ[Количество]</f>
+        <f>INDEX(Продукты!$G:$G, MATCH(ЧТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ЧТ[[#This Row],[Вес]]/ЧТ[Исх. Вес.])*ЧТ[Количество]</f>
         <v>#N/A</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2">
+      <formula1>ТипПитания</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2">
       <formula1>Продукт</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2">
-      <formula1>ТипПитания</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7494,7 +8490,7 @@
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.28515625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="35.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="45.85546875" style="1" customWidth="1"/>
     <col min="3" max="3" width="16" style="12" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="1" customWidth="1"/>
     <col min="5" max="5" width="13.5703125" style="1" customWidth="1"/>
@@ -7548,43 +8544,42 @@
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="10"/>
       <c r="B2" s="2"/>
-      <c r="C2" s="13"/>
       <c r="F2" s="1" t="e">
-        <f>INDEX(Продукты!$H:$H, MATCH(СБ[[#This Row],[Продукт]], Продукты!$A:$A, 0))</f>
+        <f>INDEX(Продукты!$H:$H, MATCH(ПТ[[#This Row],[Продукт]], Продукты!$A:$A, 0))</f>
         <v>#N/A</v>
       </c>
       <c r="G2" s="1" t="e">
-        <f>INDEX(Продукты!$B:$B, MATCH(СБ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (СБ[[#This Row],[Вес]]/100)*СБ[Количество]</f>
+        <f>INDEX(Продукты!$B:$B, MATCH(ПТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ПТ[[#This Row],[Вес]]/ПТ[Исх. Вес.])*ПТ[Количество]</f>
         <v>#N/A</v>
       </c>
       <c r="H2" s="1" t="e">
-        <f>INDEX(Продукты!$C:$C, MATCH(СБ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (СБ[[#This Row],[Вес]]/100)*СБ[Количество]</f>
+        <f>INDEX(Продукты!$C:$C, MATCH(ПТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ПТ[[#This Row],[Вес]]/ПТ[Исх. Вес.])*ПТ[Количество]</f>
         <v>#N/A</v>
       </c>
       <c r="I2" s="1" t="e">
-        <f>INDEX(Продукты!$D:$D, MATCH(СБ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (СБ[[#This Row],[Вес]]/100)*СБ[Количество]</f>
+        <f>INDEX(Продукты!$D:$D, MATCH(ПТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ПТ[[#This Row],[Вес]]/ПТ[Исх. Вес.])*ПТ[Количество]</f>
         <v>#N/A</v>
       </c>
       <c r="J2" s="1" t="e">
-        <f>INDEX(Продукты!$E:$E, MATCH(СБ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (СБ[[#This Row],[Вес]]/100)*СБ[Количество]</f>
+        <f>INDEX(Продукты!$E:$E, MATCH(ПТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ПТ[[#This Row],[Вес]]/ПТ[Исх. Вес.])*ПТ[Количество]</f>
         <v>#N/A</v>
       </c>
       <c r="K2" s="1" t="e">
-        <f>INDEX(Продукты!$F:$F, MATCH(СБ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (СБ[[#This Row],[Вес]]/100)*СБ[Количество]</f>
+        <f>INDEX(Продукты!$F:$F, MATCH(ПТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ПТ[[#This Row],[Вес]]/ПТ[Исх. Вес.])*ПТ[Количество]</f>
         <v>#N/A</v>
       </c>
       <c r="L2" s="1" t="e">
-        <f>INDEX(Продукты!$G:$G, MATCH(СБ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (СБ[[#This Row],[Вес]]/100)*СБ[Количество]</f>
+        <f>INDEX(Продукты!$G:$G, MATCH(ПТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ПТ[[#This Row],[Вес]]/ПТ[Исх. Вес.])*ПТ[Количество]</f>
         <v>#N/A</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2">
+      <formula1>Продукт</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2">
       <formula1>ТипПитания</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2">
-      <formula1>Продукт</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7657,31 +8652,138 @@
       <c r="B2" s="2"/>
       <c r="C2" s="13"/>
       <c r="F2" s="1" t="e">
+        <f>INDEX(Продукты!$H:$H, MATCH(СБ[[#This Row],[Продукт]], Продукты!$A:$A, 0))</f>
+        <v>#N/A</v>
+      </c>
+      <c r="G2" s="1" t="e">
+        <f>INDEX(Продукты!$B:$B, MATCH(СБ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (СБ[[#This Row],[Вес]]/СБ[Исх. Вес.])*СБ[Количество]</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H2" s="1" t="e">
+        <f>INDEX(Продукты!$C:$C, MATCH(СБ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (СБ[[#This Row],[Вес]]/СБ[Исх. Вес.])*СБ[Количество]</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I2" s="1" t="e">
+        <f>INDEX(Продукты!$D:$D, MATCH(СБ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (СБ[[#This Row],[Вес]]/СБ[Исх. Вес.])*СБ[Количество]</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J2" s="1" t="e">
+        <f>INDEX(Продукты!$E:$E, MATCH(СБ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (СБ[[#This Row],[Вес]]/СБ[Исх. Вес.])*СБ[Количество]</f>
+        <v>#N/A</v>
+      </c>
+      <c r="K2" s="1" t="e">
+        <f>INDEX(Продукты!$F:$F, MATCH(СБ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (СБ[[#This Row],[Вес]]/СБ[Исх. Вес.])*СБ[Количество]</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L2" s="1" t="e">
+        <f>INDEX(Продукты!$G:$G, MATCH(СБ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (СБ[[#This Row],[Вес]]/СБ[Исх. Вес.])*СБ[Количество]</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2">
+      <formula1>ТипПитания</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2">
+      <formula1>Продукт</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L2"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.28515625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="35.7109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="16" style="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5703125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="10.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="10" style="1" customWidth="1"/>
+    <col min="9" max="9" width="11.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" s="10"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="13"/>
+      <c r="F2" s="1" t="e">
         <f>INDEX(Продукты!$H:$H, MATCH(ВС[[#This Row],[Продукт]], Продукты!$A:$A, 0))</f>
         <v>#N/A</v>
       </c>
       <c r="G2" s="1" t="e">
-        <f>INDEX(Продукты!$B:$B, MATCH(ВС[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ВС[[#This Row],[Вес]]/100)*ВС[Количество]</f>
+        <f>INDEX(Продукты!$B:$B, MATCH(ВС[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ВС[[#This Row],[Вес]]/ВС[Исх. Вес.])*ВС[Количество]</f>
         <v>#N/A</v>
       </c>
       <c r="H2" s="1" t="e">
-        <f>INDEX(Продукты!$C:$C, MATCH(ВС[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ВС[[#This Row],[Вес]]/100)*ВС[Количество]</f>
+        <f>INDEX(Продукты!$C:$C, MATCH(ВС[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ВС[[#This Row],[Вес]]/ВС[Исх. Вес.])*ВС[Количество]</f>
         <v>#N/A</v>
       </c>
       <c r="I2" s="1" t="e">
-        <f>INDEX(Продукты!$D:$D, MATCH(ВС[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ВС[[#This Row],[Вес]]/100)*ВС[Количество]</f>
+        <f>INDEX(Продукты!$D:$D, MATCH(ВС[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ВС[[#This Row],[Вес]]/ВС[Исх. Вес.])*ВС[Количество]</f>
         <v>#N/A</v>
       </c>
       <c r="J2" s="1" t="e">
-        <f>INDEX(Продукты!$E:$E, MATCH(ВС[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ВС[[#This Row],[Вес]]/100)*ВС[Количество]</f>
+        <f>INDEX(Продукты!$E:$E, MATCH(ВС[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ВС[[#This Row],[Вес]]/ВС[Исх. Вес.])*ВС[Количество]</f>
         <v>#N/A</v>
       </c>
       <c r="K2" s="1" t="e">
-        <f>INDEX(Продукты!$F:$F, MATCH(ВС[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ВС[[#This Row],[Вес]]/100)*ВС[Количество]</f>
+        <f>INDEX(Продукты!$F:$F, MATCH(ВС[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ВС[[#This Row],[Вес]]/ВС[Исх. Вес.])*ВС[Количество]</f>
         <v>#N/A</v>
       </c>
       <c r="L2" s="1" t="e">
-        <f>INDEX(Продукты!$G:$G, MATCH(ВС[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ВС[[#This Row],[Вес]]/100)*ВС[Количество]</f>
+        <f>INDEX(Продукты!$G:$G, MATCH(ВС[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ВС[[#This Row],[Вес]]/ВС[Исх. Вес.])*ВС[Количество]</f>
         <v>#N/A</v>
       </c>
     </row>
@@ -7838,7 +8940,10 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" s="63">
-        <v>46113</v>
+        <v>46023</v>
+      </c>
+      <c r="Q2" s="3">
+        <v>29.6</v>
       </c>
       <c r="R2" s="3" t="e">
         <f>MIN(MAX(IF(Антропометрия[Пол]=Справочник!$C$2,86.01*LOG10(Антропометрия[Талия, см] - Антропометрия[Шея, см]) - 70.041*LOG10(Антропометрия[Рост, см]) + 36.76,163.205*LOG10(Антропометрия[Талия, см] + Антропометрия[Бедра, см] - Антропометрия[Шея, см]) - 97.684*LOG10(Антропометрия[Рост, см]) - 78.387), 5), 50)</f>
@@ -7846,7 +8951,7 @@
       </c>
       <c r="S2" s="3" t="str">
         <f>IFERROR(VLOOKUP(IF(Антропометрия[% жира (весы)]&lt;&gt;"",Антропометрия[% жира (весы)],Антропометрия[% жира, Формула Navy]), Справочник!$T$3:$V$6,3,TRUE), "Вне диапазона")</f>
-        <v>Вне диапазона</v>
+        <v>Высокий</v>
       </c>
       <c r="T2" s="3" t="e">
         <f>Антропометрия[Вес, кг]*(100-Антропометрия[% жира, Формула Navy])/100</f>
@@ -8018,7 +9123,7 @@
     </row>
     <row r="2" spans="1:24" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A2" s="65">
-        <v>46113</v>
+        <v>46023</v>
       </c>
       <c r="B2" s="17">
         <f>INDEX(Антропометрия!B:B, MATCH(Таблица4[[#This Row],[Дата]], Антропометрия!$A:$A, 0))</f>
@@ -8109,7 +9214,7 @@
     </row>
     <row r="3" spans="1:24" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A3" s="65">
-        <v>46113</v>
+        <v>46023</v>
       </c>
       <c r="B3" s="17">
         <f>INDEX(Антропометрия!B:B, MATCH(Таблица4[[#This Row],[Дата]], Антропометрия!$A:$A, 0))</f>
@@ -8223,7 +9328,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H200"/>
+  <dimension ref="A1:H185"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="74.5703125" style="54" customWidth="1"/>
@@ -8416,7 +9521,7 @@
       <c r="G16" s="62"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="50"/>
+      <c r="A17" s="51"/>
       <c r="B17" s="52"/>
       <c r="C17" s="60"/>
       <c r="D17" s="60"/>
@@ -8443,7 +9548,7 @@
       <c r="G19" s="62"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="51"/>
+      <c r="A20" s="50"/>
       <c r="B20" s="52"/>
       <c r="C20" s="60"/>
       <c r="D20" s="60"/>
@@ -8456,7 +9561,6 @@
       <c r="B21" s="52"/>
       <c r="C21" s="60"/>
       <c r="D21" s="60"/>
-      <c r="E21" s="60"/>
       <c r="F21" s="60"/>
       <c r="G21" s="62"/>
     </row>
@@ -8483,6 +9587,7 @@
       <c r="B24" s="52"/>
       <c r="C24" s="60"/>
       <c r="D24" s="60"/>
+      <c r="E24" s="60"/>
       <c r="F24" s="60"/>
       <c r="G24" s="62"/>
     </row>
@@ -9935,144 +11040,9 @@
       <c r="F185" s="60"/>
       <c r="G185" s="62"/>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A186" s="50"/>
-      <c r="B186" s="52"/>
-      <c r="C186" s="60"/>
-      <c r="D186" s="60"/>
-      <c r="E186" s="60"/>
-      <c r="F186" s="60"/>
-      <c r="G186" s="62"/>
-    </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A187" s="50"/>
-      <c r="B187" s="52"/>
-      <c r="C187" s="60"/>
-      <c r="D187" s="60"/>
-      <c r="E187" s="60"/>
-      <c r="F187" s="60"/>
-      <c r="G187" s="62"/>
-    </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A188" s="50"/>
-      <c r="B188" s="52"/>
-      <c r="C188" s="60"/>
-      <c r="D188" s="60"/>
-      <c r="E188" s="60"/>
-      <c r="F188" s="60"/>
-      <c r="G188" s="62"/>
-    </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A189" s="50"/>
-      <c r="B189" s="52"/>
-      <c r="C189" s="60"/>
-      <c r="D189" s="60"/>
-      <c r="E189" s="60"/>
-      <c r="F189" s="60"/>
-      <c r="G189" s="62"/>
-    </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A190" s="50"/>
-      <c r="B190" s="52"/>
-      <c r="C190" s="60"/>
-      <c r="D190" s="60"/>
-      <c r="E190" s="60"/>
-      <c r="F190" s="60"/>
-      <c r="G190" s="62"/>
-    </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A191" s="50"/>
-      <c r="B191" s="52"/>
-      <c r="C191" s="60"/>
-      <c r="D191" s="60"/>
-      <c r="E191" s="60"/>
-      <c r="F191" s="60"/>
-      <c r="G191" s="62"/>
-    </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A192" s="50"/>
-      <c r="B192" s="52"/>
-      <c r="C192" s="60"/>
-      <c r="D192" s="60"/>
-      <c r="E192" s="60"/>
-      <c r="F192" s="60"/>
-      <c r="G192" s="62"/>
-    </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A193" s="50"/>
-      <c r="B193" s="52"/>
-      <c r="C193" s="60"/>
-      <c r="D193" s="60"/>
-      <c r="E193" s="60"/>
-      <c r="F193" s="60"/>
-      <c r="G193" s="62"/>
-    </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A194" s="50"/>
-      <c r="B194" s="52"/>
-      <c r="C194" s="60"/>
-      <c r="D194" s="60"/>
-      <c r="E194" s="60"/>
-      <c r="F194" s="60"/>
-      <c r="G194" s="62"/>
-    </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A195" s="50"/>
-      <c r="B195" s="52"/>
-      <c r="C195" s="60"/>
-      <c r="D195" s="60"/>
-      <c r="E195" s="60"/>
-      <c r="F195" s="60"/>
-      <c r="G195" s="62"/>
-    </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A196" s="50"/>
-      <c r="B196" s="52"/>
-      <c r="C196" s="60"/>
-      <c r="D196" s="60"/>
-      <c r="E196" s="60"/>
-      <c r="F196" s="60"/>
-      <c r="G196" s="62"/>
-    </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A197" s="50"/>
-      <c r="B197" s="52"/>
-      <c r="C197" s="60"/>
-      <c r="D197" s="60"/>
-      <c r="E197" s="60"/>
-      <c r="F197" s="60"/>
-      <c r="G197" s="62"/>
-    </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A198" s="50"/>
-      <c r="B198" s="52"/>
-      <c r="C198" s="60"/>
-      <c r="D198" s="60"/>
-      <c r="E198" s="60"/>
-      <c r="F198" s="60"/>
-      <c r="G198" s="62"/>
-    </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A199" s="50"/>
-      <c r="B199" s="52"/>
-      <c r="C199" s="60"/>
-      <c r="D199" s="60"/>
-      <c r="E199" s="60"/>
-      <c r="F199" s="60"/>
-      <c r="G199" s="62"/>
-    </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A200" s="50"/>
-      <c r="B200" s="52"/>
-      <c r="C200" s="60"/>
-      <c r="D200" s="60"/>
-      <c r="E200" s="60"/>
-      <c r="F200" s="60"/>
-      <c r="G200" s="62"/>
-    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="A2:A200">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="A2:A185">
       <formula1>Рецепты</formula1>
     </dataValidation>
   </dataValidations>
@@ -10082,6 +11052,168 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:V2"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="62.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="14.85546875" style="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.140625" style="14" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.7109375" style="14" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28" style="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.42578125" style="14" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24.28515625" style="14" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="17.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="22.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="30.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="19.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="26.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="21.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="24.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="25.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="J1" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="K1" s="66" t="s">
+        <v>140</v>
+      </c>
+      <c r="L1" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="M1" s="66" t="s">
+        <v>131</v>
+      </c>
+      <c r="N1" s="66" t="s">
+        <v>132</v>
+      </c>
+      <c r="O1" s="66" t="s">
+        <v>133</v>
+      </c>
+      <c r="P1" s="66" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q1" s="66" t="s">
+        <v>135</v>
+      </c>
+      <c r="R1" s="66" t="s">
+        <v>136</v>
+      </c>
+      <c r="S1" s="66" t="s">
+        <v>137</v>
+      </c>
+      <c r="T1" s="66" t="s">
+        <v>138</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="72"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="72"/>
+      <c r="F2" s="72"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="73"/>
+      <c r="I2" s="73"/>
+      <c r="J2" s="28"/>
+      <c r="K2" s="29">
+        <f>IF(AND(СухиеПродукты[Вес готового]&lt;&gt;"",СухиеПродукты[Вес готового]&lt;&gt;""),СухиеПродукты[Вес готового]/СухиеПродукты[Вес порции сухой, г],0)</f>
+        <v>0</v>
+      </c>
+      <c r="L2" s="74">
+        <v>2.5</v>
+      </c>
+      <c r="M2" s="29">
+        <f>IF(СухиеПродукты[Коэф (выч.)]&lt;&gt;0,СухиеПродукты[Белки сухого]/СухиеПродукты[Коэф (выч.)],СухиеПродукты[Белки сухого]/СухиеПродукты[Коэф (ручной)])</f>
+        <v>0</v>
+      </c>
+      <c r="N2" s="29">
+        <f>IF(СухиеПродукты[Коэф (выч.)]&lt;&gt;0,СухиеПродукты[Жиры сухого]/СухиеПродукты[Коэф (выч.)],СухиеПродукты[Жиры сухого]/СухиеПродукты[Коэф (ручной)])</f>
+        <v>0</v>
+      </c>
+      <c r="O2" s="29">
+        <f>IF(СухиеПродукты[Коэф (выч.)]&lt;&gt;0,СухиеПродукты[Углеводы сухого]/СухиеПродукты[Коэф (выч.)],СухиеПродукты[Углеводы сухого]/СухиеПродукты[Коэф (ручной)])</f>
+        <v>0</v>
+      </c>
+      <c r="P2" s="29">
+        <f>IF(СухиеПродукты[Коэф (выч.)]&lt;&gt;0,СухиеПродукты[Клетчатка сухого]/СухиеПродукты[Коэф (выч.)],СухиеПродукты[Клетчатка сухого]/СухиеПродукты[Коэф (ручной)])</f>
+        <v>0</v>
+      </c>
+      <c r="Q2" s="29">
+        <f>IF(СухиеПродукты[Коэф (выч.)]&lt;&gt;0,СухиеПродукты[Пищевые волокна сухого]/СухиеПродукты[Коэф (выч.)],СухиеПродукты[Пищевые волокна сухого]/СухиеПродукты[Коэф (ручной)])</f>
+        <v>0</v>
+      </c>
+      <c r="R2" s="29">
+        <f>IF(СухиеПродукты[Коэф (выч.)]&lt;&gt;0,СухиеПродукты[Калории сухого]/СухиеПродукты[Коэф (выч.)],СухиеПродукты[Калории сухого]/СухиеПродукты[Коэф (ручной)])</f>
+        <v>0</v>
+      </c>
+      <c r="S2" s="29"/>
+      <c r="T2" s="29">
+        <f>IF(СухиеПродукты[Коэф (выч.)]&lt;&gt;0,СухиеПродукты[Желаемый вес готового]/СухиеПродукты[Коэф (выч.)],СухиеПродукты[Желаемый вес готового]/СухиеПродукты[Коэф (ручной)])</f>
+        <v>0</v>
+      </c>
+      <c r="U2" s="75"/>
+      <c r="V2" s="75">
+        <f>IF(СухиеПродукты[Коэф (выч.)]&lt;&gt;0,СухиеПродукты[Желаемый вес сухого]*СухиеПродукты[Коэф (выч.)],СухиеПродукты[Желаемый вес сухого]*СухиеПродукты[Коэф (ручной)])</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="54" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -10109,8 +11241,7 @@
       <c r="B2" s="16"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="27"/>
-      <c r="B3" s="16"/>
+      <c r="B3" s="27"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -10126,7 +11257,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -10184,27 +11315,27 @@
         <v>#N/A</v>
       </c>
       <c r="E2" s="1" t="e">
-        <f>INDEX(Продукты!$B:$B, MATCH(Рассчет[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (Рассчет[[#This Row],[Вес, гр]]/100)*Рассчет[Количество]</f>
+        <f>INDEX(Продукты!$B:$B, MATCH(Рассчет[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (Рассчет[[#This Row],[Вес, гр]]/Рассчет[Исх. Вес. гр])*Рассчет[Количество]</f>
         <v>#N/A</v>
       </c>
       <c r="F2" s="1" t="e">
-        <f>INDEX(Продукты!$C:$C, MATCH(Рассчет[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (Рассчет[[#This Row],[Вес, гр]]/100)*Рассчет[Количество]</f>
+        <f>INDEX(Продукты!$C:$C, MATCH(Рассчет[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (Рассчет[[#This Row],[Вес, гр]]/Рассчет[Исх. Вес. гр])*Рассчет[Количество]</f>
         <v>#N/A</v>
       </c>
       <c r="G2" s="1" t="e">
-        <f>INDEX(Продукты!$D:$D, MATCH(Рассчет[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (Рассчет[[#This Row],[Вес, гр]]/100)*Рассчет[Количество]</f>
+        <f>INDEX(Продукты!$D:$D, MATCH(Рассчет[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (Рассчет[[#This Row],[Вес, гр]]/Рассчет[Исх. Вес. гр])*Рассчет[Количество]</f>
         <v>#N/A</v>
       </c>
       <c r="H2" s="1" t="e">
-        <f>INDEX(Продукты!$E:$E, MATCH(Рассчет[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (Рассчет[[#This Row],[Вес, гр]]/100)*Рассчет[Количество]</f>
+        <f>INDEX(Продукты!$E:$E, MATCH(Рассчет[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (Рассчет[[#This Row],[Вес, гр]]/Рассчет[Исх. Вес. гр])*Рассчет[Количество]</f>
         <v>#N/A</v>
       </c>
       <c r="I2" s="1" t="e">
-        <f>INDEX(Продукты!$F:$F, MATCH(Рассчет[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (Рассчет[[#This Row],[Вес, гр]]/100)*Рассчет[Количество]</f>
+        <f>INDEX(Продукты!$F:$F, MATCH(Рассчет[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (Рассчет[[#This Row],[Вес, гр]]/Рассчет[Исх. Вес. гр])*Рассчет[Количество]</f>
         <v>#N/A</v>
       </c>
       <c r="J2" s="1" t="e">
-        <f>INDEX(Продукты!$G:$G, MATCH(Рассчет[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (Рассчет[[#This Row],[Вес, гр]]/100)*Рассчет[Количество]</f>
+        <f>INDEX(Продукты!$G:$G, MATCH(Рассчет[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (Рассчет[[#This Row],[Вес, гр]]/Рассчет[Исх. Вес. гр])*Рассчет[Количество]</f>
         <v>#N/A</v>
       </c>
     </row>
@@ -10222,7 +11353,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -10285,126 +11416,18 @@
       <c r="I2" s="3"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="27"/>
-      <c r="B3" s="16"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="28"/>
-      <c r="H3" s="29"/>
-      <c r="I3" s="29"/>
+      <c r="B3" s="27"/>
+      <c r="C3" s="72"/>
+      <c r="D3" s="72"/>
+      <c r="E3" s="72"/>
+      <c r="F3" s="72"/>
+      <c r="G3" s="72"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="73"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="54" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
-  <tableParts count="1">
-    <tablePart r:id="rId2"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L2"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="14.28515625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="35.7109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="16" style="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13.5703125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="10.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="10" style="1" customWidth="1"/>
-    <col min="9" max="9" width="11.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="20.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="10"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="13"/>
-      <c r="F2" s="1" t="e">
-        <f>INDEX(Продукты!$H:$H, MATCH(ПН[[#This Row],[Продукт]], Продукты!$A:$A, 0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G2" s="1" t="e">
-        <f>INDEX(Продукты!$B:$B, MATCH(ПН[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ПН[[#This Row],[Вес]]/100)*ПН[Количество]</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H2" s="1" t="e">
-        <f>INDEX(Продукты!$C:$C, MATCH(ПН[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ПН[[#This Row],[Вес]]/100)*ПН[Количество]</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I2" s="1" t="e">
-        <f>INDEX(Продукты!$D:$D, MATCH(ПН[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ПН[[#This Row],[Вес]]/100)*ПН[Количество]</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J2" s="1" t="e">
-        <f>INDEX(Продукты!$E:$E, MATCH(ПН[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ПН[[#This Row],[Вес]]/100)*ПН[Количество]</f>
-        <v>#N/A</v>
-      </c>
-      <c r="K2" s="1" t="e">
-        <f>INDEX(Продукты!$F:$F, MATCH(ПН[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ПН[[#This Row],[Вес]]/100)*ПН[Количество]</f>
-        <v>#N/A</v>
-      </c>
-      <c r="L2" s="1" t="e">
-        <f>INDEX(Продукты!$G:$G, MATCH(ПН[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ПН[[#This Row],[Вес]]/100)*ПН[Количество]</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2">
-      <formula1>Продукт</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2">
-      <formula1>ТипПитания</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
   <tableParts count="1">
     <tablePart r:id="rId2"/>
   </tableParts>
@@ -10422,11 +11445,12 @@
     <col min="4" max="4" width="10" style="1" customWidth="1"/>
     <col min="5" max="5" width="13.5703125" style="1" customWidth="1"/>
     <col min="6" max="6" width="10.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="10" style="1" customWidth="1"/>
-    <col min="9" max="9" width="11.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="20.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10" style="3" customWidth="1"/>
+    <col min="9" max="9" width="11.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.140625" style="14" bestFit="1" customWidth="1"/>
     <col min="13" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
@@ -10449,65 +11473,64 @@
       <c r="F1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="10"/>
       <c r="B2" s="2"/>
-      <c r="C2" s="13"/>
       <c r="F2" s="1" t="e">
-        <f>INDEX(Продукты!$H:$H, MATCH(ВТ[[#This Row],[Продукт]], Продукты!$A:$A, 0))</f>
+        <f>INDEX(Продукты!$H:$H, MATCH(ПН[[#This Row],[Продукт]], Продукты!$A:$A, 0))</f>
         <v>#N/A</v>
       </c>
-      <c r="G2" s="1" t="e">
-        <f>INDEX(Продукты!$B:$B, MATCH(ВТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ВТ[[#This Row],[Вес]]/100)*ВТ[Количество]</f>
+      <c r="G2" s="3" t="e">
+        <f>INDEX(Продукты!$B:$B, MATCH(ПН[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ПН[[#This Row],[Вес]]/ПН[Исх. Вес.])*ПН[Количество]</f>
         <v>#N/A</v>
       </c>
-      <c r="H2" s="1" t="e">
-        <f>INDEX(Продукты!$C:$C, MATCH(ВТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ВТ[[#This Row],[Вес]]/100)*ВТ[Количество]</f>
+      <c r="H2" s="3" t="e">
+        <f>INDEX(Продукты!$C:$C, MATCH(ПН[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ПН[[#This Row],[Вес]]/ПН[Исх. Вес.])*ПН[Количество]</f>
         <v>#N/A</v>
       </c>
-      <c r="I2" s="1" t="e">
-        <f>INDEX(Продукты!$D:$D, MATCH(ВТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ВТ[[#This Row],[Вес]]/100)*ВТ[Количество]</f>
+      <c r="I2" s="3" t="e">
+        <f>INDEX(Продукты!$D:$D, MATCH(ПН[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ПН[[#This Row],[Вес]]/ПН[Исх. Вес.])*ПН[Количество]</f>
         <v>#N/A</v>
       </c>
-      <c r="J2" s="1" t="e">
-        <f>INDEX(Продукты!$E:$E, MATCH(ВТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ВТ[[#This Row],[Вес]]/100)*ВТ[Количество]</f>
+      <c r="J2" s="3" t="e">
+        <f>INDEX(Продукты!$E:$E, MATCH(ПН[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ПН[[#This Row],[Вес]]/ПН[Исх. Вес.])*ПН[Количество]</f>
         <v>#N/A</v>
       </c>
-      <c r="K2" s="1" t="e">
-        <f>INDEX(Продукты!$F:$F, MATCH(ВТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ВТ[[#This Row],[Вес]]/100)*ВТ[Количество]</f>
+      <c r="K2" s="3" t="e">
+        <f>INDEX(Продукты!$F:$F, MATCH(ПН[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ПН[[#This Row],[Вес]]/ПН[Исх. Вес.])*ПН[Количество]</f>
         <v>#N/A</v>
       </c>
-      <c r="L2" s="1" t="e">
-        <f>INDEX(Продукты!$G:$G, MATCH(ВТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ВТ[[#This Row],[Вес]]/100)*ВТ[Количество]</f>
+      <c r="L2" s="3" t="e">
+        <f>INDEX(Продукты!$G:$G, MATCH(ПН[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ПН[[#This Row],[Вес]]/ПН[Исх. Вес.])*ПН[Количество]</f>
         <v>#N/A</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2">
+      <formula1>Продукт</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2">
       <formula1>ТипПитания</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2">
-      <formula1>Продукт</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/files/кбжу-example.xlsx
+++ b/files/кбжу-example.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Справочник" sheetId="20" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="148">
   <si>
     <t>Белки</t>
   </si>
@@ -474,6 +474,15 @@
   </si>
   <si>
     <t>Пищевая ценность, гр</t>
+  </si>
+  <si>
+    <t>Вес, мл.</t>
+  </si>
+  <si>
+    <t>Плотность</t>
+  </si>
+  <si>
+    <t>Вес, мл</t>
   </si>
 </sst>
 </file>
@@ -511,11 +520,15 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
     </font>
     <font>
       <sz val="12"/>
@@ -835,7 +848,187 @@
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="331">
+  <dxfs count="341">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -6610,7 +6803,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="Антропометрия" displayName="Антропометрия" ref="A1:AE2" totalsRowShown="0" headerRowDxfId="330" dataDxfId="329">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="Антропометрия" displayName="Антропометрия" ref="A1:AE2" totalsRowShown="0" headerRowDxfId="340" dataDxfId="339">
   <autoFilter ref="A1:AE2">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -6645,61 +6838,61 @@
     <filterColumn colId="30" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="31">
-    <tableColumn id="1" name="Дата" dataDxfId="328"/>
-    <tableColumn id="2" name="Вес, кг" dataDxfId="327"/>
-    <tableColumn id="3" name="Рост, см" dataDxfId="326"/>
-    <tableColumn id="4" name="Возраст, лет" dataDxfId="325"/>
-    <tableColumn id="5" name="Пол" dataDxfId="324"/>
-    <tableColumn id="6" name="Шея, см" dataDxfId="323"/>
-    <tableColumn id="7" name="Грудь, см" dataDxfId="322"/>
-    <tableColumn id="8" name="Плечи, см" dataDxfId="321"/>
-    <tableColumn id="9" name="Рука правая, см" dataDxfId="320"/>
-    <tableColumn id="10" name="Рука левая, см" dataDxfId="319"/>
-    <tableColumn id="11" name="Талия, см" dataDxfId="318"/>
-    <tableColumn id="12" name="Бедра, см" dataDxfId="317"/>
-    <tableColumn id="13" name="Бедро левое, см" dataDxfId="316"/>
-    <tableColumn id="14" name="Бедро правое, см" dataDxfId="315"/>
-    <tableColumn id="15" name="Икра правая, см" dataDxfId="314"/>
-    <tableColumn id="16" name="Икра левая, см" dataDxfId="313"/>
+    <tableColumn id="1" name="Дата" dataDxfId="338"/>
+    <tableColumn id="2" name="Вес, кг" dataDxfId="337"/>
+    <tableColumn id="3" name="Рост, см" dataDxfId="336"/>
+    <tableColumn id="4" name="Возраст, лет" dataDxfId="335"/>
+    <tableColumn id="5" name="Пол" dataDxfId="334"/>
+    <tableColumn id="6" name="Шея, см" dataDxfId="333"/>
+    <tableColumn id="7" name="Грудь, см" dataDxfId="332"/>
+    <tableColumn id="8" name="Плечи, см" dataDxfId="331"/>
+    <tableColumn id="9" name="Рука правая, см" dataDxfId="330"/>
+    <tableColumn id="10" name="Рука левая, см" dataDxfId="329"/>
+    <tableColumn id="11" name="Талия, см" dataDxfId="328"/>
+    <tableColumn id="12" name="Бедра, см" dataDxfId="327"/>
+    <tableColumn id="13" name="Бедро левое, см" dataDxfId="326"/>
+    <tableColumn id="14" name="Бедро правое, см" dataDxfId="325"/>
+    <tableColumn id="15" name="Икра правая, см" dataDxfId="324"/>
+    <tableColumn id="16" name="Икра левая, см" dataDxfId="323"/>
     <tableColumn id="23" name="% жира (весы)"/>
-    <tableColumn id="17" name="% жира, Формула Navy" dataDxfId="312">
+    <tableColumn id="17" name="% жира, Формула Navy" dataDxfId="322">
       <calculatedColumnFormula>MIN(MAX(IF(Антропометрия[Пол]=Справочник!$C$2,86.01*LOG10(Антропометрия[Талия, см] - Антропометрия[Шея, см]) - 70.041*LOG10(Антропометрия[Рост, см]) + 36.76,163.205*LOG10(Антропометрия[Талия, см] + Антропометрия[Бедра, см] - Антропометрия[Шея, см]) - 97.684*LOG10(Антропометрия[Рост, см]) - 78.387), 5), 50)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="25" name="Уровень % жира" dataDxfId="311">
+    <tableColumn id="25" name="Уровень % жира" dataDxfId="321">
       <calculatedColumnFormula>IFERROR(VLOOKUP(IF(Антропометрия[% жира (весы)]&lt;&gt;"",Антропометрия[% жира (весы)],Антропометрия[% жира, Формула Navy]), Справочник!$T$3:$V$6,3,TRUE), "Вне диапазона")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" name="Мышечная масса, кг" dataDxfId="310">
+    <tableColumn id="18" name="Мышечная масса, кг" dataDxfId="320">
       <calculatedColumnFormula>Антропометрия[Вес, кг]*(100-Антропометрия[% жира, Формула Navy])/100</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="26" name="Уровень мышечной массы" dataDxfId="309">
+    <tableColumn id="26" name="Уровень мышечной массы" dataDxfId="319">
       <calculatedColumnFormula>VLOOKUP(Антропометрия[Мышечная масса, кг], Справочник!$X$3:$Z$5, 3, TRUE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" name="Висцеральный жир (рассчет)" dataDxfId="308">
+    <tableColumn id="19" name="Висцеральный жир (рассчет)" dataDxfId="318">
       <calculatedColumnFormula>MIN(20, MAX(0, ( Антропометрия[Талия, см] / Антропометрия[Рост, см] - 0.4 ) * 50 ))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="27" name="Висцеральный жир (уровень)" dataDxfId="307">
+    <tableColumn id="27" name="Висцеральный жир (уровень)" dataDxfId="317">
       <calculatedColumnFormula>VLOOKUP(Антропометрия[Висцеральный жир (рассчет)], Справочник!$AB$3:$AD$5, 3, TRUE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" name="Костная масса, кг (рассчет)" dataDxfId="306">
+    <tableColumn id="20" name="Костная масса, кг (рассчет)" dataDxfId="316">
       <calculatedColumnFormula>IF(Антропометрия[Пол]=Справочник!$C$2, Антропометрия[Вес, кг] * 0.04, Антропометрия[Вес, кг] * 0.03)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="28" name="Костная масса, кг, уровень" dataDxfId="305">
+    <tableColumn id="28" name="Костная масса, кг, уровень" dataDxfId="315">
       <calculatedColumnFormula>VLOOKUP(Антропометрия[Костная масса, кг (рассчет)], Справочник!$AF$3:$AH$5, 3, TRUE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" name="ИМТ (расчёт)" dataDxfId="304">
+    <tableColumn id="21" name="ИМТ (расчёт)" dataDxfId="314">
       <calculatedColumnFormula>Антропометрия[[#This Row],[Вес, кг]]/((Антропометрия[[#This Row],[Рост, см]]/100)^2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="29" name="ИМТ (уровень)" dataDxfId="303">
+    <tableColumn id="29" name="ИМТ (уровень)" dataDxfId="313">
       <calculatedColumnFormula>VLOOKUP(Антропометрия[ИМТ (расчёт)], Справочник!$AJ$3:$AL$5, 3, TRUE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" name="BMR (расчёт)" dataDxfId="302">
+    <tableColumn id="22" name="BMR (расчёт)" dataDxfId="312">
       <calculatedColumnFormula>10*Антропометрия[[#This Row],[Вес, кг]]+6.25*Антропометрия[[#This Row],[Рост, см]]-5*Антропометрия[[#This Row],[Возраст, лет]]+IF(Антропометрия[[#This Row],[Пол]]=Справочник!$C$2,5,-161)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="30" name="BMR (уровень)" dataDxfId="301">
+    <tableColumn id="30" name="BMR (уровень)" dataDxfId="311">
       <calculatedColumnFormula>VLOOKUP(Антропометрия[BMR (расчёт)], Справочник!$AN$3:$AP$5, 3, TRUE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="24" name="BMR (с весов)" dataDxfId="300"/>
-    <tableColumn id="31" name="BMR (с весов, уровень)" dataDxfId="299">
+    <tableColumn id="24" name="BMR (с весов)" dataDxfId="310"/>
+    <tableColumn id="31" name="BMR (с весов, уровень)" dataDxfId="309">
       <calculatedColumnFormula>IF(Антропометрия[BMR (с весов)]&lt;&gt;"",VLOOKUP(Антропометрия[BMR (с весов)], Справочник!$AN$3:$AP$5, 3, TRUE),"")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6708,7 +6901,7 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="ЧТ" displayName="ЧТ" ref="A1:L2" headerRowDxfId="103" dataDxfId="102">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="ВТ" displayName="ВТ" ref="A1:L2" headerRowDxfId="165" dataDxfId="164">
   <autoFilter ref="A1:L2">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -6724,38 +6917,38 @@
     <filterColumn colId="11" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="12">
-    <tableColumn id="11" name="Тип питания" dataDxfId="101" totalsRowDxfId="100"/>
-    <tableColumn id="1" name="Продукт" totalsRowLabel="Итог" dataDxfId="99" totalsRowDxfId="98"/>
-    <tableColumn id="12" name="Время приёма" dataDxfId="97" totalsRowDxfId="96"/>
-    <tableColumn id="9" name="Вес" totalsRowFunction="custom" dataDxfId="95" totalsRowDxfId="94">
-      <totalsRowFormula>SUMPRODUCT(ЧТ[Вес], ЧТ[Количество])</totalsRowFormula>
+    <tableColumn id="11" name="Тип питания" dataDxfId="163" totalsRowDxfId="162"/>
+    <tableColumn id="1" name="Продукт" totalsRowLabel="Итог" dataDxfId="161" totalsRowDxfId="160"/>
+    <tableColumn id="12" name="Время приёма" dataDxfId="159" totalsRowDxfId="158"/>
+    <tableColumn id="9" name="Вес" totalsRowFunction="custom" dataDxfId="157" totalsRowDxfId="156">
+      <totalsRowFormula>SUMPRODUCT(ВТ[Вес], ВТ[Количество])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="10" name="Количество" totalsRowFunction="sum" dataDxfId="93" totalsRowDxfId="92"/>
-    <tableColumn id="2" name="Исх. Вес." totalsRowFunction="sum" dataDxfId="91" totalsRowDxfId="90">
-      <calculatedColumnFormula>INDEX(Продукты!$H:$H, MATCH(ЧТ[[#This Row],[Продукт]], Продукты!$A:$A, 0))</calculatedColumnFormula>
+    <tableColumn id="10" name="Количество" totalsRowFunction="sum" dataDxfId="155" totalsRowDxfId="154"/>
+    <tableColumn id="2" name="Исх. Вес." totalsRowFunction="sum" dataDxfId="153" totalsRowDxfId="152">
+      <calculatedColumnFormula>INDEX(Продукты!$H:$H, MATCH(ВТ[[#This Row],[Продукт]], Продукты!$A:$A, 0))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" name="Белки" totalsRowFunction="custom" dataDxfId="89" totalsRowDxfId="88">
-      <calculatedColumnFormula>INDEX(Продукты!$B:$B, MATCH(ЧТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ЧТ[[#This Row],[Вес]]/ЧТ[Исх. Вес.])*ЧТ[Количество]</calculatedColumnFormula>
-      <totalsRowFormula>SUMPRODUCT(ЧТ[Белки], ЧТ[Количество])</totalsRowFormula>
+    <tableColumn id="3" name="Белки" totalsRowFunction="custom" dataDxfId="151" totalsRowDxfId="150">
+      <calculatedColumnFormula>INDEX(Продукты!$B:$B, MATCH(ВТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ВТ[[#This Row],[Вес]]/ВТ[Исх. Вес.])*ВТ[Количество]</calculatedColumnFormula>
+      <totalsRowFormula>SUMPRODUCT(ВТ[Белки], ВТ[Количество])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="4" name="Жиры" totalsRowFunction="custom" dataDxfId="87" totalsRowDxfId="86">
-      <calculatedColumnFormula>INDEX(Продукты!$C:$C, MATCH(ЧТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ЧТ[[#This Row],[Вес]]/ЧТ[Исх. Вес.])*ЧТ[Количество]</calculatedColumnFormula>
-      <totalsRowFormula>SUMPRODUCT(ЧТ[Жиры], ЧТ[Количество])</totalsRowFormula>
+    <tableColumn id="4" name="Жиры" totalsRowFunction="custom" dataDxfId="149" totalsRowDxfId="148">
+      <calculatedColumnFormula>INDEX(Продукты!$C:$C, MATCH(ВТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ВТ[[#This Row],[Вес]]/ВТ[Исх. Вес.])*ВТ[Количество]</calculatedColumnFormula>
+      <totalsRowFormula>SUMPRODUCT(ВТ[Жиры], ВТ[Количество])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" name="Углеводы" totalsRowFunction="custom" dataDxfId="85" totalsRowDxfId="84">
-      <calculatedColumnFormula>INDEX(Продукты!$D:$D, MATCH(ЧТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ЧТ[[#This Row],[Вес]]/ЧТ[Исх. Вес.])*ЧТ[Количество]</calculatedColumnFormula>
-      <totalsRowFormula>SUMPRODUCT(ЧТ[Углеводы], ЧТ[Количество])</totalsRowFormula>
+    <tableColumn id="5" name="Углеводы" totalsRowFunction="custom" dataDxfId="147" totalsRowDxfId="146">
+      <calculatedColumnFormula>INDEX(Продукты!$D:$D, MATCH(ВТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ВТ[[#This Row],[Вес]]/ВТ[Исх. Вес.])*ВТ[Количество]</calculatedColumnFormula>
+      <totalsRowFormula>SUMPRODUCT(ВТ[Углеводы], ВТ[Количество])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="6" name="Клетчатка" totalsRowFunction="custom" dataDxfId="83" totalsRowDxfId="82">
-      <calculatedColumnFormula>INDEX(Продукты!$E:$E, MATCH(ЧТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ЧТ[[#This Row],[Вес]]/ЧТ[Исх. Вес.])*ЧТ[Количество]</calculatedColumnFormula>
-      <totalsRowFormula>SUMPRODUCT(ЧТ[Клетчатка], ЧТ[Количество])</totalsRowFormula>
+    <tableColumn id="6" name="Клетчатка" totalsRowFunction="custom" dataDxfId="145" totalsRowDxfId="144">
+      <calculatedColumnFormula>INDEX(Продукты!$E:$E, MATCH(ВТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ВТ[[#This Row],[Вес]]/ВТ[Исх. Вес.])*ВТ[Количество]</calculatedColumnFormula>
+      <totalsRowFormula>SUMPRODUCT(ВТ[Клетчатка], ВТ[Количество])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="7" name="Пищевые волокна" totalsRowFunction="custom" dataDxfId="81" totalsRowDxfId="80">
-      <calculatedColumnFormula>INDEX(Продукты!$F:$F, MATCH(ЧТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ЧТ[[#This Row],[Вес]]/ЧТ[Исх. Вес.])*ЧТ[Количество]</calculatedColumnFormula>
-      <totalsRowFormula>SUMPRODUCT(ЧТ[Пищевые волокна], ЧТ[Количество])</totalsRowFormula>
+    <tableColumn id="7" name="Пищевые волокна" totalsRowFunction="custom" dataDxfId="143" totalsRowDxfId="142">
+      <calculatedColumnFormula>INDEX(Продукты!$F:$F, MATCH(ВТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ВТ[[#This Row],[Вес]]/ВТ[Исх. Вес.])*ВТ[Количество]</calculatedColumnFormula>
+      <totalsRowFormula>SUMPRODUCT(ВТ[Пищевые волокна], ВТ[Количество])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="8" name="Калории, ккл" totalsRowFunction="sum" dataDxfId="79" totalsRowDxfId="78">
-      <calculatedColumnFormula>INDEX(Продукты!$G:$G, MATCH(ЧТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ЧТ[[#This Row],[Вес]]/ЧТ[Исх. Вес.])*ЧТ[Количество]</calculatedColumnFormula>
+    <tableColumn id="8" name="Калории, ккл" totalsRowFunction="sum" dataDxfId="141" totalsRowDxfId="140">
+      <calculatedColumnFormula>INDEX(Продукты!$G:$G, MATCH(ВТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ВТ[[#This Row],[Вес]]/ВТ[Исх. Вес.])*ВТ[Количество]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -6763,7 +6956,7 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="ПТ" displayName="ПТ" ref="A1:L2" headerRowDxfId="77" dataDxfId="76">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="СР" displayName="СР" ref="A1:L2" headerRowDxfId="139" dataDxfId="138">
   <autoFilter ref="A1:L2">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -6779,38 +6972,38 @@
     <filterColumn colId="11" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="12">
-    <tableColumn id="11" name="Тип питания" dataDxfId="75" totalsRowDxfId="74"/>
-    <tableColumn id="1" name="Продукт" totalsRowLabel="Итог" dataDxfId="73" totalsRowDxfId="72"/>
-    <tableColumn id="12" name="Время приёма" dataDxfId="71" totalsRowDxfId="70"/>
-    <tableColumn id="9" name="Вес" totalsRowFunction="custom" dataDxfId="69" totalsRowDxfId="68">
-      <totalsRowFormula>SUMPRODUCT(ПТ[Вес], ПТ[Количество])</totalsRowFormula>
+    <tableColumn id="11" name="Тип питания" dataDxfId="137" totalsRowDxfId="136"/>
+    <tableColumn id="1" name="Продукт" totalsRowLabel="Итог" dataDxfId="135" totalsRowDxfId="134"/>
+    <tableColumn id="12" name="Время приёма" dataDxfId="133" totalsRowDxfId="132"/>
+    <tableColumn id="9" name="Вес" totalsRowFunction="custom" dataDxfId="131" totalsRowDxfId="130">
+      <totalsRowFormula>SUMPRODUCT(СР[Вес], СР[Количество])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="10" name="Количество" totalsRowFunction="sum" dataDxfId="67" totalsRowDxfId="66"/>
-    <tableColumn id="2" name="Исх. Вес." totalsRowFunction="sum" dataDxfId="65" totalsRowDxfId="64">
-      <calculatedColumnFormula>INDEX(Продукты!$H:$H, MATCH(ПТ[[#This Row],[Продукт]], Продукты!$A:$A, 0))</calculatedColumnFormula>
+    <tableColumn id="10" name="Количество" totalsRowFunction="sum" dataDxfId="129" totalsRowDxfId="128"/>
+    <tableColumn id="2" name="Исх. Вес." totalsRowFunction="sum" dataDxfId="127" totalsRowDxfId="126">
+      <calculatedColumnFormula>INDEX(Продукты!$H:$H, MATCH(СР[[#This Row],[Продукт]], Продукты!$A:$A, 0))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" name="Белки" totalsRowFunction="custom" dataDxfId="63" totalsRowDxfId="62">
-      <calculatedColumnFormula>INDEX(Продукты!$B:$B, MATCH(ПТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ПТ[[#This Row],[Вес]]/ПТ[Исх. Вес.])*ПТ[Количество]</calculatedColumnFormula>
-      <totalsRowFormula>SUMPRODUCT(ПТ[Белки], ПТ[Количество])</totalsRowFormula>
+    <tableColumn id="3" name="Белки" totalsRowFunction="custom" dataDxfId="125" totalsRowDxfId="124">
+      <calculatedColumnFormula>INDEX(Продукты!$B:$B, MATCH(СР[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (СР[[#This Row],[Вес]]/СР[Исх. Вес.])*СР[Количество]</calculatedColumnFormula>
+      <totalsRowFormula>SUMPRODUCT(СР[Белки], СР[Количество])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="4" name="Жиры" totalsRowFunction="custom" dataDxfId="61" totalsRowDxfId="60">
-      <calculatedColumnFormula>INDEX(Продукты!$C:$C, MATCH(ПТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ПТ[[#This Row],[Вес]]/ПТ[Исх. Вес.])*ПТ[Количество]</calculatedColumnFormula>
-      <totalsRowFormula>SUMPRODUCT(ПТ[Жиры], ПТ[Количество])</totalsRowFormula>
+    <tableColumn id="4" name="Жиры" totalsRowFunction="custom" dataDxfId="123" totalsRowDxfId="122">
+      <calculatedColumnFormula>INDEX(Продукты!$C:$C, MATCH(СР[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (СР[[#This Row],[Вес]]/СР[Исх. Вес.])*СР[Количество]</calculatedColumnFormula>
+      <totalsRowFormula>SUMPRODUCT(СР[Жиры], СР[Количество])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" name="Углеводы" totalsRowFunction="custom" dataDxfId="59" totalsRowDxfId="58">
-      <calculatedColumnFormula>INDEX(Продукты!$D:$D, MATCH(ПТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ПТ[[#This Row],[Вес]]/ПТ[Исх. Вес.])*ПТ[Количество]</calculatedColumnFormula>
-      <totalsRowFormula>SUMPRODUCT(ПТ[Углеводы], ПТ[Количество])</totalsRowFormula>
+    <tableColumn id="5" name="Углеводы" totalsRowFunction="custom" dataDxfId="121" totalsRowDxfId="120">
+      <calculatedColumnFormula>INDEX(Продукты!$D:$D, MATCH(СР[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (СР[[#This Row],[Вес]]/СР[Исх. Вес.])*СР[Количество]</calculatedColumnFormula>
+      <totalsRowFormula>SUMPRODUCT(СР[Углеводы], СР[Количество])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="6" name="Клетчатка" totalsRowFunction="custom" dataDxfId="57" totalsRowDxfId="56">
-      <calculatedColumnFormula>INDEX(Продукты!$E:$E, MATCH(ПТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ПТ[[#This Row],[Вес]]/ПТ[Исх. Вес.])*ПТ[Количество]</calculatedColumnFormula>
-      <totalsRowFormula>SUMPRODUCT(ПТ[Клетчатка], ПТ[Количество])</totalsRowFormula>
+    <tableColumn id="6" name="Клетчатка" totalsRowFunction="custom" dataDxfId="119" totalsRowDxfId="118">
+      <calculatedColumnFormula>INDEX(Продукты!$E:$E, MATCH(СР[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (СР[[#This Row],[Вес]]/СР[Исх. Вес.])*СР[Количество]</calculatedColumnFormula>
+      <totalsRowFormula>SUMPRODUCT(СР[Клетчатка], СР[Количество])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="7" name="Пищевые волокна" totalsRowFunction="custom" dataDxfId="55" totalsRowDxfId="54">
-      <calculatedColumnFormula>INDEX(Продукты!$F:$F, MATCH(ПТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ПТ[[#This Row],[Вес]]/ПТ[Исх. Вес.])*ПТ[Количество]</calculatedColumnFormula>
-      <totalsRowFormula>SUMPRODUCT(ПТ[Пищевые волокна], ПТ[Количество])</totalsRowFormula>
+    <tableColumn id="7" name="Пищевые волокна" totalsRowFunction="custom" dataDxfId="117" totalsRowDxfId="116">
+      <calculatedColumnFormula>INDEX(Продукты!$F:$F, MATCH(СР[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (СР[[#This Row],[Вес]]/СР[Исх. Вес.])*СР[Количество]</calculatedColumnFormula>
+      <totalsRowFormula>SUMPRODUCT(СР[Пищевые волокна], СР[Количество])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="8" name="Калории, ккл" totalsRowFunction="sum" dataDxfId="53" totalsRowDxfId="52">
-      <calculatedColumnFormula>INDEX(Продукты!$G:$G, MATCH(ПТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ПТ[[#This Row],[Вес]]/ПТ[Исх. Вес.])*ПТ[Количество]</calculatedColumnFormula>
+    <tableColumn id="8" name="Калории, ккл" totalsRowFunction="sum" dataDxfId="115" totalsRowDxfId="114">
+      <calculatedColumnFormula>INDEX(Продукты!$G:$G, MATCH(СР[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (СР[[#This Row],[Вес]]/СР[Исх. Вес.])*СР[Количество]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -6818,7 +7011,7 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="СБ" displayName="СБ" ref="A1:L2" headerRowDxfId="51" dataDxfId="50">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="ЧТ" displayName="ЧТ" ref="A1:L2" headerRowDxfId="113" dataDxfId="112">
   <autoFilter ref="A1:L2">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -6834,38 +7027,38 @@
     <filterColumn colId="11" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="12">
-    <tableColumn id="11" name="Тип питания" dataDxfId="49" totalsRowDxfId="48"/>
-    <tableColumn id="1" name="Продукт" totalsRowLabel="Итог" dataDxfId="47" totalsRowDxfId="46"/>
-    <tableColumn id="12" name="Время приёма" dataDxfId="45" totalsRowDxfId="44"/>
-    <tableColumn id="9" name="Вес" totalsRowFunction="custom" dataDxfId="43" totalsRowDxfId="42">
-      <totalsRowFormula>SUMPRODUCT(СБ[Вес], СБ[Количество])</totalsRowFormula>
+    <tableColumn id="11" name="Тип питания" dataDxfId="111" totalsRowDxfId="110"/>
+    <tableColumn id="1" name="Продукт" totalsRowLabel="Итог" dataDxfId="109" totalsRowDxfId="108"/>
+    <tableColumn id="12" name="Время приёма" dataDxfId="107" totalsRowDxfId="106"/>
+    <tableColumn id="9" name="Вес" totalsRowFunction="custom" dataDxfId="105" totalsRowDxfId="104">
+      <totalsRowFormula>SUMPRODUCT(ЧТ[Вес], ЧТ[Количество])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="10" name="Количество" totalsRowFunction="sum" dataDxfId="41" totalsRowDxfId="40"/>
-    <tableColumn id="2" name="Исх. Вес." totalsRowFunction="sum" dataDxfId="39" totalsRowDxfId="38">
-      <calculatedColumnFormula>INDEX(Продукты!$H:$H, MATCH(СБ[[#This Row],[Продукт]], Продукты!$A:$A, 0))</calculatedColumnFormula>
+    <tableColumn id="10" name="Количество" totalsRowFunction="sum" dataDxfId="103" totalsRowDxfId="102"/>
+    <tableColumn id="2" name="Исх. Вес." totalsRowFunction="sum" dataDxfId="101" totalsRowDxfId="100">
+      <calculatedColumnFormula>INDEX(Продукты!$H:$H, MATCH(ЧТ[[#This Row],[Продукт]], Продукты!$A:$A, 0))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" name="Белки" totalsRowFunction="custom" dataDxfId="37" totalsRowDxfId="36">
-      <calculatedColumnFormula>INDEX(Продукты!$B:$B, MATCH(СБ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (СБ[[#This Row],[Вес]]/СБ[Исх. Вес.])*СБ[Количество]</calculatedColumnFormula>
-      <totalsRowFormula>SUMPRODUCT(СБ[Белки], СБ[Количество])</totalsRowFormula>
+    <tableColumn id="3" name="Белки" totalsRowFunction="custom" dataDxfId="99" totalsRowDxfId="98">
+      <calculatedColumnFormula>INDEX(Продукты!$B:$B, MATCH(ЧТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ЧТ[[#This Row],[Вес]]/ЧТ[Исх. Вес.])*ЧТ[Количество]</calculatedColumnFormula>
+      <totalsRowFormula>SUMPRODUCT(ЧТ[Белки], ЧТ[Количество])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="4" name="Жиры" totalsRowFunction="custom" dataDxfId="35" totalsRowDxfId="34">
-      <calculatedColumnFormula>INDEX(Продукты!$C:$C, MATCH(СБ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (СБ[[#This Row],[Вес]]/СБ[Исх. Вес.])*СБ[Количество]</calculatedColumnFormula>
-      <totalsRowFormula>SUMPRODUCT(СБ[Жиры], СБ[Количество])</totalsRowFormula>
+    <tableColumn id="4" name="Жиры" totalsRowFunction="custom" dataDxfId="97" totalsRowDxfId="96">
+      <calculatedColumnFormula>INDEX(Продукты!$C:$C, MATCH(ЧТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ЧТ[[#This Row],[Вес]]/ЧТ[Исх. Вес.])*ЧТ[Количество]</calculatedColumnFormula>
+      <totalsRowFormula>SUMPRODUCT(ЧТ[Жиры], ЧТ[Количество])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" name="Углеводы" totalsRowFunction="custom" dataDxfId="33" totalsRowDxfId="32">
-      <calculatedColumnFormula>INDEX(Продукты!$D:$D, MATCH(СБ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (СБ[[#This Row],[Вес]]/СБ[Исх. Вес.])*СБ[Количество]</calculatedColumnFormula>
-      <totalsRowFormula>SUMPRODUCT(СБ[Углеводы], СБ[Количество])</totalsRowFormula>
+    <tableColumn id="5" name="Углеводы" totalsRowFunction="custom" dataDxfId="95" totalsRowDxfId="94">
+      <calculatedColumnFormula>INDEX(Продукты!$D:$D, MATCH(ЧТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ЧТ[[#This Row],[Вес]]/ЧТ[Исх. Вес.])*ЧТ[Количество]</calculatedColumnFormula>
+      <totalsRowFormula>SUMPRODUCT(ЧТ[Углеводы], ЧТ[Количество])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="6" name="Клетчатка" totalsRowFunction="custom" dataDxfId="31" totalsRowDxfId="30">
-      <calculatedColumnFormula>INDEX(Продукты!$E:$E, MATCH(СБ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (СБ[[#This Row],[Вес]]/СБ[Исх. Вес.])*СБ[Количество]</calculatedColumnFormula>
-      <totalsRowFormula>SUMPRODUCT(СБ[Клетчатка], СБ[Количество])</totalsRowFormula>
+    <tableColumn id="6" name="Клетчатка" totalsRowFunction="custom" dataDxfId="93" totalsRowDxfId="92">
+      <calculatedColumnFormula>INDEX(Продукты!$E:$E, MATCH(ЧТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ЧТ[[#This Row],[Вес]]/ЧТ[Исх. Вес.])*ЧТ[Количество]</calculatedColumnFormula>
+      <totalsRowFormula>SUMPRODUCT(ЧТ[Клетчатка], ЧТ[Количество])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="7" name="Пищевые волокна" totalsRowFunction="custom" dataDxfId="29" totalsRowDxfId="28">
-      <calculatedColumnFormula>INDEX(Продукты!$F:$F, MATCH(СБ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (СБ[[#This Row],[Вес]]/СБ[Исх. Вес.])*СБ[Количество]</calculatedColumnFormula>
-      <totalsRowFormula>SUMPRODUCT(СБ[Пищевые волокна], СБ[Количество])</totalsRowFormula>
+    <tableColumn id="7" name="Пищевые волокна" totalsRowFunction="custom" dataDxfId="91" totalsRowDxfId="90">
+      <calculatedColumnFormula>INDEX(Продукты!$F:$F, MATCH(ЧТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ЧТ[[#This Row],[Вес]]/ЧТ[Исх. Вес.])*ЧТ[Количество]</calculatedColumnFormula>
+      <totalsRowFormula>SUMPRODUCT(ЧТ[Пищевые волокна], ЧТ[Количество])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="8" name="Калории, ккл" totalsRowFunction="sum" dataDxfId="27" totalsRowDxfId="26">
-      <calculatedColumnFormula>INDEX(Продукты!$G:$G, MATCH(СБ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (СБ[[#This Row],[Вес]]/СБ[Исх. Вес.])*СБ[Количество]</calculatedColumnFormula>
+    <tableColumn id="8" name="Калории, ккл" totalsRowFunction="sum" dataDxfId="89" totalsRowDxfId="88">
+      <calculatedColumnFormula>INDEX(Продукты!$G:$G, MATCH(ЧТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ЧТ[[#This Row],[Вес]]/ЧТ[Исх. Вес.])*ЧТ[Количество]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -6873,7 +7066,7 @@
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="ВС" displayName="ВС" ref="A1:L2" headerRowDxfId="25" dataDxfId="24">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="ПТ" displayName="ПТ" ref="A1:L2" headerRowDxfId="87" dataDxfId="86">
   <autoFilter ref="A1:L2">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -6889,37 +7082,147 @@
     <filterColumn colId="11" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="12">
-    <tableColumn id="11" name="Тип питания" dataDxfId="23" totalsRowDxfId="22"/>
-    <tableColumn id="1" name="Продукт" totalsRowLabel="Итог" dataDxfId="21" totalsRowDxfId="20"/>
-    <tableColumn id="12" name="Время приёма" dataDxfId="19" totalsRowDxfId="18"/>
-    <tableColumn id="9" name="Вес" totalsRowFunction="custom" dataDxfId="17" totalsRowDxfId="16">
+    <tableColumn id="11" name="Тип питания" dataDxfId="85" totalsRowDxfId="84"/>
+    <tableColumn id="1" name="Продукт" totalsRowLabel="Итог" dataDxfId="83" totalsRowDxfId="82"/>
+    <tableColumn id="12" name="Время приёма" dataDxfId="81" totalsRowDxfId="80"/>
+    <tableColumn id="9" name="Вес" totalsRowFunction="custom" dataDxfId="79" totalsRowDxfId="78">
+      <totalsRowFormula>SUMPRODUCT(ПТ[Вес], ПТ[Количество])</totalsRowFormula>
+    </tableColumn>
+    <tableColumn id="10" name="Количество" totalsRowFunction="sum" dataDxfId="77" totalsRowDxfId="76"/>
+    <tableColumn id="2" name="Исх. Вес." totalsRowFunction="sum" dataDxfId="75" totalsRowDxfId="74">
+      <calculatedColumnFormula>INDEX(Продукты!$H:$H, MATCH(ПТ[[#This Row],[Продукт]], Продукты!$A:$A, 0))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="3" name="Белки" totalsRowFunction="custom" dataDxfId="73" totalsRowDxfId="72">
+      <calculatedColumnFormula>INDEX(Продукты!$B:$B, MATCH(ПТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ПТ[[#This Row],[Вес]]/ПТ[Исх. Вес.])*ПТ[Количество]</calculatedColumnFormula>
+      <totalsRowFormula>SUMPRODUCT(ПТ[Белки], ПТ[Количество])</totalsRowFormula>
+    </tableColumn>
+    <tableColumn id="4" name="Жиры" totalsRowFunction="custom" dataDxfId="71" totalsRowDxfId="70">
+      <calculatedColumnFormula>INDEX(Продукты!$C:$C, MATCH(ПТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ПТ[[#This Row],[Вес]]/ПТ[Исх. Вес.])*ПТ[Количество]</calculatedColumnFormula>
+      <totalsRowFormula>SUMPRODUCT(ПТ[Жиры], ПТ[Количество])</totalsRowFormula>
+    </tableColumn>
+    <tableColumn id="5" name="Углеводы" totalsRowFunction="custom" dataDxfId="69" totalsRowDxfId="68">
+      <calculatedColumnFormula>INDEX(Продукты!$D:$D, MATCH(ПТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ПТ[[#This Row],[Вес]]/ПТ[Исх. Вес.])*ПТ[Количество]</calculatedColumnFormula>
+      <totalsRowFormula>SUMPRODUCT(ПТ[Углеводы], ПТ[Количество])</totalsRowFormula>
+    </tableColumn>
+    <tableColumn id="6" name="Клетчатка" totalsRowFunction="custom" dataDxfId="67" totalsRowDxfId="66">
+      <calculatedColumnFormula>INDEX(Продукты!$E:$E, MATCH(ПТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ПТ[[#This Row],[Вес]]/ПТ[Исх. Вес.])*ПТ[Количество]</calculatedColumnFormula>
+      <totalsRowFormula>SUMPRODUCT(ПТ[Клетчатка], ПТ[Количество])</totalsRowFormula>
+    </tableColumn>
+    <tableColumn id="7" name="Пищевые волокна" totalsRowFunction="custom" dataDxfId="65" totalsRowDxfId="64">
+      <calculatedColumnFormula>INDEX(Продукты!$F:$F, MATCH(ПТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ПТ[[#This Row],[Вес]]/ПТ[Исх. Вес.])*ПТ[Количество]</calculatedColumnFormula>
+      <totalsRowFormula>SUMPRODUCT(ПТ[Пищевые волокна], ПТ[Количество])</totalsRowFormula>
+    </tableColumn>
+    <tableColumn id="8" name="Калории, ккл" totalsRowFunction="sum" dataDxfId="63" totalsRowDxfId="62">
+      <calculatedColumnFormula>INDEX(Продукты!$G:$G, MATCH(ПТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ПТ[[#This Row],[Вес]]/ПТ[Исх. Вес.])*ПТ[Количество]</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="СБ" displayName="СБ" ref="A1:L2" headerRowDxfId="61" dataDxfId="60">
+  <autoFilter ref="A1:L2">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+    <filterColumn colId="3" hiddenButton="1"/>
+    <filterColumn colId="4" hiddenButton="1"/>
+    <filterColumn colId="5" hiddenButton="1"/>
+    <filterColumn colId="6" hiddenButton="1"/>
+    <filterColumn colId="7" hiddenButton="1"/>
+    <filterColumn colId="8" hiddenButton="1"/>
+    <filterColumn colId="9" hiddenButton="1"/>
+    <filterColumn colId="10" hiddenButton="1"/>
+    <filterColumn colId="11" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="12">
+    <tableColumn id="11" name="Тип питания" dataDxfId="59" totalsRowDxfId="58"/>
+    <tableColumn id="1" name="Продукт" totalsRowLabel="Итог" dataDxfId="57" totalsRowDxfId="56"/>
+    <tableColumn id="12" name="Время приёма" dataDxfId="55" totalsRowDxfId="54"/>
+    <tableColumn id="9" name="Вес" totalsRowFunction="custom" dataDxfId="53" totalsRowDxfId="52">
+      <totalsRowFormula>SUMPRODUCT(СБ[Вес], СБ[Количество])</totalsRowFormula>
+    </tableColumn>
+    <tableColumn id="10" name="Количество" totalsRowFunction="sum" dataDxfId="51" totalsRowDxfId="50"/>
+    <tableColumn id="2" name="Исх. Вес." totalsRowFunction="sum" dataDxfId="49" totalsRowDxfId="48">
+      <calculatedColumnFormula>INDEX(Продукты!$H:$H, MATCH(СБ[[#This Row],[Продукт]], Продукты!$A:$A, 0))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="3" name="Белки" totalsRowFunction="custom" dataDxfId="47" totalsRowDxfId="46">
+      <calculatedColumnFormula>INDEX(Продукты!$B:$B, MATCH(СБ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (СБ[[#This Row],[Вес]]/СБ[Исх. Вес.])*СБ[Количество]</calculatedColumnFormula>
+      <totalsRowFormula>SUMPRODUCT(СБ[Белки], СБ[Количество])</totalsRowFormula>
+    </tableColumn>
+    <tableColumn id="4" name="Жиры" totalsRowFunction="custom" dataDxfId="45" totalsRowDxfId="44">
+      <calculatedColumnFormula>INDEX(Продукты!$C:$C, MATCH(СБ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (СБ[[#This Row],[Вес]]/СБ[Исх. Вес.])*СБ[Количество]</calculatedColumnFormula>
+      <totalsRowFormula>SUMPRODUCT(СБ[Жиры], СБ[Количество])</totalsRowFormula>
+    </tableColumn>
+    <tableColumn id="5" name="Углеводы" totalsRowFunction="custom" dataDxfId="43" totalsRowDxfId="42">
+      <calculatedColumnFormula>INDEX(Продукты!$D:$D, MATCH(СБ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (СБ[[#This Row],[Вес]]/СБ[Исх. Вес.])*СБ[Количество]</calculatedColumnFormula>
+      <totalsRowFormula>SUMPRODUCT(СБ[Углеводы], СБ[Количество])</totalsRowFormula>
+    </tableColumn>
+    <tableColumn id="6" name="Клетчатка" totalsRowFunction="custom" dataDxfId="41" totalsRowDxfId="40">
+      <calculatedColumnFormula>INDEX(Продукты!$E:$E, MATCH(СБ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (СБ[[#This Row],[Вес]]/СБ[Исх. Вес.])*СБ[Количество]</calculatedColumnFormula>
+      <totalsRowFormula>SUMPRODUCT(СБ[Клетчатка], СБ[Количество])</totalsRowFormula>
+    </tableColumn>
+    <tableColumn id="7" name="Пищевые волокна" totalsRowFunction="custom" dataDxfId="39" totalsRowDxfId="38">
+      <calculatedColumnFormula>INDEX(Продукты!$F:$F, MATCH(СБ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (СБ[[#This Row],[Вес]]/СБ[Исх. Вес.])*СБ[Количество]</calculatedColumnFormula>
+      <totalsRowFormula>SUMPRODUCT(СБ[Пищевые волокна], СБ[Количество])</totalsRowFormula>
+    </tableColumn>
+    <tableColumn id="8" name="Калории, ккл" totalsRowFunction="sum" dataDxfId="37" totalsRowDxfId="36">
+      <calculatedColumnFormula>INDEX(Продукты!$G:$G, MATCH(СБ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (СБ[[#This Row],[Вес]]/СБ[Исх. Вес.])*СБ[Количество]</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="ВС" displayName="ВС" ref="A1:L2" headerRowDxfId="35" dataDxfId="34">
+  <autoFilter ref="A1:L2">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+    <filterColumn colId="3" hiddenButton="1"/>
+    <filterColumn colId="4" hiddenButton="1"/>
+    <filterColumn colId="5" hiddenButton="1"/>
+    <filterColumn colId="6" hiddenButton="1"/>
+    <filterColumn colId="7" hiddenButton="1"/>
+    <filterColumn colId="8" hiddenButton="1"/>
+    <filterColumn colId="9" hiddenButton="1"/>
+    <filterColumn colId="10" hiddenButton="1"/>
+    <filterColumn colId="11" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="12">
+    <tableColumn id="11" name="Тип питания" dataDxfId="33" totalsRowDxfId="32"/>
+    <tableColumn id="1" name="Продукт" totalsRowLabel="Итог" dataDxfId="31" totalsRowDxfId="30"/>
+    <tableColumn id="12" name="Время приёма" dataDxfId="29" totalsRowDxfId="28"/>
+    <tableColumn id="9" name="Вес" totalsRowFunction="custom" dataDxfId="27" totalsRowDxfId="26">
       <totalsRowFormula>SUMPRODUCT(ВС[Вес], ВС[Количество])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="10" name="Количество" totalsRowFunction="sum" dataDxfId="15" totalsRowDxfId="14"/>
-    <tableColumn id="2" name="Исх. Вес." totalsRowFunction="sum" dataDxfId="13" totalsRowDxfId="12">
+    <tableColumn id="10" name="Количество" totalsRowFunction="sum" dataDxfId="25" totalsRowDxfId="24"/>
+    <tableColumn id="2" name="Исх. Вес." totalsRowFunction="sum" dataDxfId="23" totalsRowDxfId="22">
       <calculatedColumnFormula>INDEX(Продукты!$H:$H, MATCH(ВС[[#This Row],[Продукт]], Продукты!$A:$A, 0))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" name="Белки" totalsRowFunction="custom" dataDxfId="11" totalsRowDxfId="10">
+    <tableColumn id="3" name="Белки" totalsRowFunction="custom" dataDxfId="21" totalsRowDxfId="20">
       <calculatedColumnFormula>INDEX(Продукты!$B:$B, MATCH(ВС[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ВС[[#This Row],[Вес]]/ВС[Исх. Вес.])*ВС[Количество]</calculatedColumnFormula>
       <totalsRowFormula>SUMPRODUCT(ВС[Белки], ВС[Количество])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="4" name="Жиры" totalsRowFunction="custom" dataDxfId="9" totalsRowDxfId="8">
+    <tableColumn id="4" name="Жиры" totalsRowFunction="custom" dataDxfId="19" totalsRowDxfId="18">
       <calculatedColumnFormula>INDEX(Продукты!$C:$C, MATCH(ВС[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ВС[[#This Row],[Вес]]/ВС[Исх. Вес.])*ВС[Количество]</calculatedColumnFormula>
       <totalsRowFormula>SUMPRODUCT(ВС[Жиры], ВС[Количество])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" name="Углеводы" totalsRowFunction="custom" dataDxfId="7" totalsRowDxfId="6">
+    <tableColumn id="5" name="Углеводы" totalsRowFunction="custom" dataDxfId="17" totalsRowDxfId="16">
       <calculatedColumnFormula>INDEX(Продукты!$D:$D, MATCH(ВС[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ВС[[#This Row],[Вес]]/ВС[Исх. Вес.])*ВС[Количество]</calculatedColumnFormula>
       <totalsRowFormula>SUMPRODUCT(ВС[Углеводы], ВС[Количество])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="6" name="Клетчатка" totalsRowFunction="custom" dataDxfId="5" totalsRowDxfId="4">
+    <tableColumn id="6" name="Клетчатка" totalsRowFunction="custom" dataDxfId="15" totalsRowDxfId="14">
       <calculatedColumnFormula>INDEX(Продукты!$E:$E, MATCH(ВС[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ВС[[#This Row],[Вес]]/ВС[Исх. Вес.])*ВС[Количество]</calculatedColumnFormula>
       <totalsRowFormula>SUMPRODUCT(ВС[Клетчатка], ВС[Количество])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="7" name="Пищевые волокна" totalsRowFunction="custom" dataDxfId="3" totalsRowDxfId="2">
+    <tableColumn id="7" name="Пищевые волокна" totalsRowFunction="custom" dataDxfId="13" totalsRowDxfId="12">
       <calculatedColumnFormula>INDEX(Продукты!$F:$F, MATCH(ВС[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ВС[[#This Row],[Вес]]/ВС[Исх. Вес.])*ВС[Количество]</calculatedColumnFormula>
       <totalsRowFormula>SUMPRODUCT(ВС[Пищевые волокна], ВС[Количество])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="8" name="Калории, ккл" totalsRowFunction="sum" dataDxfId="1" totalsRowDxfId="0">
+    <tableColumn id="8" name="Калории, ккл" totalsRowFunction="sum" dataDxfId="11" totalsRowDxfId="10">
       <calculatedColumnFormula>INDEX(Продукты!$G:$G, MATCH(ВС[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ВС[[#This Row],[Вес]]/ВС[Исх. Вес.])*ВС[Количество]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6956,58 +7259,58 @@
     <filterColumn colId="23" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="24">
-    <tableColumn id="20" name="Дата" dataDxfId="298"/>
-    <tableColumn id="1" name="Вес" dataDxfId="297"/>
-    <tableColumn id="2" name="Рост" dataDxfId="296"/>
-    <tableColumn id="3" name="Возраст" dataDxfId="295"/>
-    <tableColumn id="4" name="Пол" dataDxfId="294"/>
-    <tableColumn id="5" name="Активность" dataDxfId="293"/>
-    <tableColumn id="6" name="Цель" dataDxfId="292"/>
-    <tableColumn id="17" name="TDEE коэфф." dataDxfId="291">
+    <tableColumn id="20" name="Дата" dataDxfId="308"/>
+    <tableColumn id="1" name="Вес" dataDxfId="307"/>
+    <tableColumn id="2" name="Рост" dataDxfId="306"/>
+    <tableColumn id="3" name="Возраст" dataDxfId="305"/>
+    <tableColumn id="4" name="Пол" dataDxfId="304"/>
+    <tableColumn id="5" name="Активность" dataDxfId="303"/>
+    <tableColumn id="6" name="Цель" dataDxfId="302"/>
+    <tableColumn id="17" name="TDEE коэфф." dataDxfId="301">
       <calculatedColumnFormula>VLOOKUP(Таблица4[[#This Row],[Активность]], Справочник!$E$2:$F$7, 2, 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="23" name="Коэф белки низ" dataDxfId="290">
+    <tableColumn id="23" name="Коэф белки низ" dataDxfId="300">
       <calculatedColumnFormula>VLOOKUP(Таблица4[[#This Row],[Активность]], Справочник!$H$2:$J$7, 2, 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" name="Коэф белки верх" dataDxfId="289">
+    <tableColumn id="22" name="Коэф белки верх" dataDxfId="299">
       <calculatedColumnFormula>VLOOKUP(Таблица4[[#This Row],[Активность]], Справочник!$H$2:$J$7, 3, 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" name="Коэф.Жир низ" dataDxfId="288"/>
-    <tableColumn id="18" name="Коэф. Жир верх" dataDxfId="287"/>
-    <tableColumn id="25" name="Кэф дифицита низ" dataDxfId="286">
+    <tableColumn id="19" name="Коэф.Жир низ" dataDxfId="298"/>
+    <tableColumn id="18" name="Коэф. Жир верх" dataDxfId="297"/>
+    <tableColumn id="25" name="Кэф дифицита низ" dataDxfId="296">
       <calculatedColumnFormula>VLOOKUP(Таблица4[[#This Row],[Цель]], Справочник!$P$2:$R$5, 2, 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="24" name="Коэф дифицита верх" dataDxfId="285">
+    <tableColumn id="24" name="Коэф дифицита верх" dataDxfId="295">
       <calculatedColumnFormula>VLOOKUP(Таблица4[[#This Row],[Цель]], Справочник!$P$2:$R$5, 3, 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" name="BMR" dataDxfId="284">
+    <tableColumn id="7" name="BMR" dataDxfId="294">
       <calculatedColumnFormula>10*Таблица4[Вес]+6.25*Таблица4[Рост]-5*Таблица4[Возраст]+IF(Таблица4[[#This Row],[Пол]]=Справочник!$C$2,5,-161)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" name="TDEE" dataDxfId="283">
+    <tableColumn id="8" name="TDEE" dataDxfId="293">
       <calculatedColumnFormula>Таблица4[BMR]*Таблица4[TDEE коэфф.]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" name="Белки низ" dataDxfId="282">
+    <tableColumn id="11" name="Белки низ" dataDxfId="292">
       <calculatedColumnFormula>Таблица4[Вес]*Таблица4[Коэф белки низ]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" name="Белки верх" dataDxfId="281">
+    <tableColumn id="12" name="Белки верх" dataDxfId="291">
       <calculatedColumnFormula>Таблица4[Вес]*Таблица4[Коэф белки верх]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" name="Жиры низ" dataDxfId="280">
+    <tableColumn id="13" name="Жиры низ" dataDxfId="290">
       <calculatedColumnFormula>Таблица4[Вес]*Таблица4[Коэф.Жир низ]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" name="Жиры верх" dataDxfId="279">
+    <tableColumn id="14" name="Жиры верх" dataDxfId="289">
       <calculatedColumnFormula>Таблица4[Вес]*Таблица4[Коэф. Жир верх]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" name="Углеводы низ" dataDxfId="278">
+    <tableColumn id="15" name="Углеводы низ" dataDxfId="288">
       <calculatedColumnFormula>(Таблица4[Калории мин]-(Таблица4[Белки верх]*4+Таблица4[Жиры верх]*9))/4</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" name="Углеводы верх" dataDxfId="277">
+    <tableColumn id="16" name="Углеводы верх" dataDxfId="287">
       <calculatedColumnFormula>(Таблица4[Калории макс]-(Таблица4[Белки низ]*4+Таблица4[Жиры низ]*9))/4</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" name="Калории мин" dataDxfId="276">
+    <tableColumn id="9" name="Калории мин" dataDxfId="286">
       <calculatedColumnFormula>Таблица4[TDEE]-Таблица4[Коэф дифицита верх]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" name="Калории макс" dataDxfId="275">
+    <tableColumn id="10" name="Калории макс" dataDxfId="285">
       <calculatedColumnFormula>Таблица4[TDEE]-Таблица4[Кэф дифицита низ]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7016,7 +7319,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="СухиеПродукты" displayName="СухиеПродукты" ref="A1:V2" headerRowDxfId="274" dataDxfId="273">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="СухиеПродукты" displayName="СухиеПродукты" ref="A1:V2" headerRowDxfId="284" dataDxfId="283">
   <autoFilter ref="A1:V2">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -7042,44 +7345,44 @@
     <filterColumn colId="21" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="22">
-    <tableColumn id="1" name="Название" totalsRowLabel="Итог" dataDxfId="272"/>
-    <tableColumn id="4" name="Белки сухого" dataDxfId="271" totalsRowDxfId="270"/>
-    <tableColumn id="5" name="Жиры сухого" dataDxfId="269" totalsRowDxfId="268"/>
-    <tableColumn id="6" name="Углеводы сухого" dataDxfId="267" totalsRowDxfId="266"/>
-    <tableColumn id="7" name="Клетчатка сухого" dataDxfId="265" totalsRowDxfId="264"/>
-    <tableColumn id="8" name="Пищевые волокна сухого" dataDxfId="263" totalsRowDxfId="262"/>
-    <tableColumn id="9" name="Калории сухого" dataDxfId="261" totalsRowDxfId="260"/>
-    <tableColumn id="10" name="Пищевая ценность, гр" dataDxfId="259" totalsRowDxfId="258"/>
-    <tableColumn id="20" name="Вес порции сухой, г" dataDxfId="257" totalsRowDxfId="256"/>
-    <tableColumn id="2" name="Вес готового" dataDxfId="255" totalsRowDxfId="254"/>
-    <tableColumn id="3" name="Коэф (выч.)" dataDxfId="253" totalsRowDxfId="252">
+    <tableColumn id="1" name="Название" totalsRowLabel="Итог" dataDxfId="282"/>
+    <tableColumn id="4" name="Белки сухого" dataDxfId="281" totalsRowDxfId="280"/>
+    <tableColumn id="5" name="Жиры сухого" dataDxfId="279" totalsRowDxfId="278"/>
+    <tableColumn id="6" name="Углеводы сухого" dataDxfId="277" totalsRowDxfId="276"/>
+    <tableColumn id="7" name="Клетчатка сухого" dataDxfId="275" totalsRowDxfId="274"/>
+    <tableColumn id="8" name="Пищевые волокна сухого" dataDxfId="273" totalsRowDxfId="272"/>
+    <tableColumn id="9" name="Калории сухого" dataDxfId="271" totalsRowDxfId="270"/>
+    <tableColumn id="10" name="Пищевая ценность, гр" dataDxfId="269" totalsRowDxfId="268"/>
+    <tableColumn id="20" name="Вес порции сухой, г" dataDxfId="267" totalsRowDxfId="266"/>
+    <tableColumn id="2" name="Вес готового" dataDxfId="265" totalsRowDxfId="264"/>
+    <tableColumn id="3" name="Коэф (выч.)" dataDxfId="263" totalsRowDxfId="262">
       <calculatedColumnFormula>IF(AND(СухиеПродукты[Вес готового]&lt;&gt;"",СухиеПродукты[Вес готового]&lt;&gt;""),СухиеПродукты[Вес готового]/СухиеПродукты[Вес порции сухой, г],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" name="Коэф (ручной)" dataDxfId="251" totalsRowDxfId="250"/>
-    <tableColumn id="11" name="Белки готового" dataDxfId="249" totalsRowDxfId="248">
+    <tableColumn id="19" name="Коэф (ручной)" dataDxfId="261" totalsRowDxfId="260"/>
+    <tableColumn id="11" name="Белки готового" dataDxfId="259" totalsRowDxfId="258">
       <calculatedColumnFormula>IF(СухиеПродукты[Коэф (выч.)]&lt;&gt;0,СухиеПродукты[Белки сухого]/СухиеПродукты[Коэф (выч.)],СухиеПродукты[Белки сухого]/СухиеПродукты[Коэф (ручной)])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" name="Жиры готового" dataDxfId="247" totalsRowDxfId="246">
+    <tableColumn id="12" name="Жиры готового" dataDxfId="257" totalsRowDxfId="256">
       <calculatedColumnFormula>IF(СухиеПродукты[Коэф (выч.)]&lt;&gt;0,СухиеПродукты[Жиры сухого]/СухиеПродукты[Коэф (выч.)],СухиеПродукты[Жиры сухого]/СухиеПродукты[Коэф (ручной)])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" name="Углеводы готового" dataDxfId="245" totalsRowDxfId="244">
+    <tableColumn id="13" name="Углеводы готового" dataDxfId="255" totalsRowDxfId="254">
       <calculatedColumnFormula>IF(СухиеПродукты[Коэф (выч.)]&lt;&gt;0,СухиеПродукты[Углеводы сухого]/СухиеПродукты[Коэф (выч.)],СухиеПродукты[Углеводы сухого]/СухиеПродукты[Коэф (ручной)])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" name="Клетчатка готового" dataDxfId="243" totalsRowDxfId="242">
+    <tableColumn id="14" name="Клетчатка готового" dataDxfId="253" totalsRowDxfId="252">
       <calculatedColumnFormula>IF(СухиеПродукты[Коэф (выч.)]&lt;&gt;0,СухиеПродукты[Клетчатка сухого]/СухиеПродукты[Коэф (выч.)],СухиеПродукты[Клетчатка сухого]/СухиеПродукты[Коэф (ручной)])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" name="Пищевые волокна готового" dataDxfId="241" totalsRowDxfId="240">
+    <tableColumn id="15" name="Пищевые волокна готового" dataDxfId="251" totalsRowDxfId="250">
       <calculatedColumnFormula>IF(СухиеПродукты[Коэф (выч.)]&lt;&gt;0,СухиеПродукты[Пищевые волокна сухого]/СухиеПродукты[Коэф (выч.)],СухиеПродукты[Пищевые волокна сухого]/СухиеПродукты[Коэф (ручной)])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" name="Калории готового" dataDxfId="239" totalsRowDxfId="238">
+    <tableColumn id="16" name="Калории готового" dataDxfId="249" totalsRowDxfId="248">
       <calculatedColumnFormula>IF(СухиеПродукты[Коэф (выч.)]&lt;&gt;0,СухиеПродукты[Калории сухого]/СухиеПродукты[Коэф (выч.)],СухиеПродукты[Калории сухого]/СухиеПродукты[Коэф (ручной)])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" name="Желаемый вес готового" dataDxfId="237" totalsRowDxfId="236"/>
-    <tableColumn id="18" name="Нужный вес сухого" dataDxfId="235" totalsRowDxfId="234">
+    <tableColumn id="17" name="Желаемый вес готового" dataDxfId="247" totalsRowDxfId="246"/>
+    <tableColumn id="18" name="Нужный вес сухого" dataDxfId="245" totalsRowDxfId="244">
       <calculatedColumnFormula>IF(СухиеПродукты[Коэф (выч.)]&lt;&gt;0,СухиеПродукты[Желаемый вес готового]/СухиеПродукты[Коэф (выч.)],СухиеПродукты[Желаемый вес готового]/СухиеПродукты[Коэф (ручной)])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" name="Желаемый вес сухого" dataDxfId="233" totalsRowDxfId="232"/>
-    <tableColumn id="22" name="Итоговый вес готового" dataDxfId="231" totalsRowDxfId="230">
+    <tableColumn id="21" name="Желаемый вес сухого" dataDxfId="243" totalsRowDxfId="242"/>
+    <tableColumn id="22" name="Итоговый вес готового" dataDxfId="241" totalsRowDxfId="240">
       <calculatedColumnFormula>IF(СухиеПродукты[Коэф (выч.)]&lt;&gt;0,СухиеПродукты[Желаемый вес сухого]*СухиеПродукты[Коэф (выч.)],СухиеПродукты[Желаемый вес сухого]*СухиеПродукты[Коэф (ручной)])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7088,21 +7391,21 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Состав" displayName="Состав" ref="A1:B3" headerRowDxfId="229" dataDxfId="228">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Состав" displayName="Состав" ref="A1:B3" headerRowDxfId="239" dataDxfId="238">
   <autoFilter ref="A1:B3">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" name="Продукт" totalsRowLabel="Итог" dataDxfId="227" totalsRowDxfId="226"/>
-    <tableColumn id="2" name="Состав" dataDxfId="225" totalsRowDxfId="224"/>
+    <tableColumn id="1" name="Продукт" totalsRowLabel="Итог" dataDxfId="237" totalsRowDxfId="236"/>
+    <tableColumn id="2" name="Состав" dataDxfId="235" totalsRowDxfId="234"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Рассчет" displayName="Рассчет" ref="A1:J2" headerRowDxfId="223" dataDxfId="222">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Рассчет" displayName="Рассчет" ref="A1:J2" headerRowDxfId="233" dataDxfId="232">
   <autoFilter ref="A1:J2">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -7116,33 +7419,33 @@
     <filterColumn colId="9" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="10">
-    <tableColumn id="1" name="Продукт" totalsRowLabel="Итог" dataDxfId="221" totalsRowDxfId="220"/>
-    <tableColumn id="9" name="Вес, гр" totalsRowFunction="sum" dataDxfId="219" totalsRowDxfId="218"/>
-    <tableColumn id="10" name="Количество" totalsRowFunction="sum" dataDxfId="217" totalsRowDxfId="216"/>
-    <tableColumn id="2" name="Исх. Вес. гр" totalsRowFunction="sum" dataDxfId="215" totalsRowDxfId="214">
+    <tableColumn id="1" name="Продукт" totalsRowLabel="Итог" dataDxfId="231" totalsRowDxfId="230"/>
+    <tableColumn id="9" name="Вес, гр" totalsRowFunction="sum" dataDxfId="229" totalsRowDxfId="228"/>
+    <tableColumn id="10" name="Количество" totalsRowFunction="sum" dataDxfId="227" totalsRowDxfId="226"/>
+    <tableColumn id="2" name="Исх. Вес. гр" totalsRowFunction="sum" dataDxfId="225" totalsRowDxfId="224">
       <calculatedColumnFormula>INDEX(Продукты!$H:$H, MATCH(Рассчет[[#This Row],[Продукт]], Продукты!$A:$A, 0))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" name="Белки" totalsRowFunction="custom" dataDxfId="213" totalsRowDxfId="212">
+    <tableColumn id="3" name="Белки" totalsRowFunction="custom" dataDxfId="223" totalsRowDxfId="222">
       <calculatedColumnFormula>INDEX(Продукты!$B:$B, MATCH(Рассчет[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (Рассчет[[#This Row],[Вес, гр]]/Рассчет[Исх. Вес. гр])*Рассчет[Количество]</calculatedColumnFormula>
       <totalsRowFormula>SUMPRODUCT(Рассчет[Белки], Рассчет[Количество])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="4" name="Жиры" totalsRowFunction="custom" dataDxfId="211" totalsRowDxfId="210">
+    <tableColumn id="4" name="Жиры" totalsRowFunction="custom" dataDxfId="221" totalsRowDxfId="220">
       <calculatedColumnFormula>INDEX(Продукты!$C:$C, MATCH(Рассчет[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (Рассчет[[#This Row],[Вес, гр]]/Рассчет[Исх. Вес. гр])*Рассчет[Количество]</calculatedColumnFormula>
       <totalsRowFormula>SUMPRODUCT(Рассчет[Жиры], Рассчет[Количество])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" name="Углеводы" totalsRowFunction="custom" dataDxfId="209" totalsRowDxfId="208">
+    <tableColumn id="5" name="Углеводы" totalsRowFunction="custom" dataDxfId="219" totalsRowDxfId="218">
       <calculatedColumnFormula>INDEX(Продукты!$D:$D, MATCH(Рассчет[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (Рассчет[[#This Row],[Вес, гр]]/Рассчет[Исх. Вес. гр])*Рассчет[Количество]</calculatedColumnFormula>
       <totalsRowFormula>SUMPRODUCT(Рассчет[Углеводы], Рассчет[Количество])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="6" name="Клетчатка" totalsRowFunction="custom" dataDxfId="207" totalsRowDxfId="206">
+    <tableColumn id="6" name="Клетчатка" totalsRowFunction="custom" dataDxfId="217" totalsRowDxfId="216">
       <calculatedColumnFormula>INDEX(Продукты!$E:$E, MATCH(Рассчет[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (Рассчет[[#This Row],[Вес, гр]]/Рассчет[Исх. Вес. гр])*Рассчет[Количество]</calculatedColumnFormula>
       <totalsRowFormula>SUMPRODUCT(Рассчет[Клетчатка], Рассчет[Количество])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="7" name="Пищевые волокна" totalsRowFunction="custom" dataDxfId="205" totalsRowDxfId="204">
+    <tableColumn id="7" name="Пищевые волокна" totalsRowFunction="custom" dataDxfId="215" totalsRowDxfId="214">
       <calculatedColumnFormula>INDEX(Продукты!$F:$F, MATCH(Рассчет[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (Рассчет[[#This Row],[Вес, гр]]/Рассчет[Исх. Вес. гр])*Рассчет[Количество]</calculatedColumnFormula>
       <totalsRowFormula>SUMPRODUCT(Рассчет[Пищевые волокна], Рассчет[Количество])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="8" name="Калории, ккл" totalsRowFunction="sum" dataDxfId="203" totalsRowDxfId="202">
+    <tableColumn id="8" name="Калории, ккл" totalsRowFunction="sum" dataDxfId="213" totalsRowDxfId="212">
       <calculatedColumnFormula>INDEX(Продукты!$G:$G, MATCH(Рассчет[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (Рассчет[[#This Row],[Вес, гр]]/Рассчет[Исх. Вес. гр])*Рассчет[Количество]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7151,7 +7454,47 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="Рецепт" displayName="Рецепт" ref="A1:I3" headerRowDxfId="201" dataDxfId="200">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="МлГр" displayName="МлГр" ref="L1:N2" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
+  <autoFilter ref="L1:N2">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="3">
+    <tableColumn id="1" name="Вес, мл." dataDxfId="7"/>
+    <tableColumn id="3" name="Плотность" dataDxfId="6">
+      <calculatedColumnFormula>INDEX(Продукты!$I:$I, MATCH(Рассчет[Продукт], Продукты!$A:$A, 0))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="2" name="Вес, гр" dataDxfId="5">
+      <calculatedColumnFormula>МлГр[Вес, мл.]*МлГр[Плотность]</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="ГрМл" displayName="ГрМл" ref="P1:R2" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
+  <autoFilter ref="P1:R2">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="3">
+    <tableColumn id="1" name="Вес, гр" dataDxfId="2"/>
+    <tableColumn id="3" name="Плотность" dataDxfId="1">
+      <calculatedColumnFormula>INDEX(Продукты!$I:$I, MATCH(Рассчет[Продукт], Продукты!$A:$A, 0))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="2" name="Вес, мл" dataDxfId="0">
+      <calculatedColumnFormula>ГрМл[Вес, гр]/ГрМл[Плотность]</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="Рецепт" displayName="Рецепт" ref="A1:I3" headerRowDxfId="211" dataDxfId="210">
   <autoFilter ref="A1:I3">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -7164,22 +7507,22 @@
     <filterColumn colId="8" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="9">
-    <tableColumn id="1" name="Название" totalsRowLabel="Итог" dataDxfId="199" totalsRowDxfId="198"/>
-    <tableColumn id="2" name="Рецепт" dataDxfId="197" totalsRowDxfId="196"/>
-    <tableColumn id="4" name="Белки" dataDxfId="195" totalsRowDxfId="194"/>
-    <tableColumn id="5" name="Жиры" dataDxfId="193" totalsRowDxfId="192"/>
-    <tableColumn id="6" name="Углеводы" dataDxfId="191" totalsRowDxfId="190"/>
-    <tableColumn id="7" name="Клетчатка" dataDxfId="189" totalsRowDxfId="188"/>
-    <tableColumn id="8" name="Пищевые волокна" dataDxfId="187" totalsRowDxfId="186"/>
-    <tableColumn id="9" name="Калории" dataDxfId="185" totalsRowDxfId="184"/>
-    <tableColumn id="10" name="Вес" dataDxfId="183" totalsRowDxfId="182"/>
+    <tableColumn id="1" name="Название" totalsRowLabel="Итог" dataDxfId="209" totalsRowDxfId="208"/>
+    <tableColumn id="2" name="Рецепт" dataDxfId="207" totalsRowDxfId="206"/>
+    <tableColumn id="4" name="Белки" dataDxfId="205" totalsRowDxfId="204"/>
+    <tableColumn id="5" name="Жиры" dataDxfId="203" totalsRowDxfId="202"/>
+    <tableColumn id="6" name="Углеводы" dataDxfId="201" totalsRowDxfId="200"/>
+    <tableColumn id="7" name="Клетчатка" dataDxfId="199" totalsRowDxfId="198"/>
+    <tableColumn id="8" name="Пищевые волокна" dataDxfId="197" totalsRowDxfId="196"/>
+    <tableColumn id="9" name="Калории" dataDxfId="195" totalsRowDxfId="194"/>
+    <tableColumn id="10" name="Вес" dataDxfId="193" totalsRowDxfId="192"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
-<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="ПН" displayName="ПН" ref="A1:L2" headerRowDxfId="181" dataDxfId="180">
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="ПН" displayName="ПН" ref="A1:L2" headerRowDxfId="191" dataDxfId="190">
   <autoFilter ref="A1:L2">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -7195,148 +7538,38 @@
     <filterColumn colId="11" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="12">
-    <tableColumn id="11" name="Тип питания" dataDxfId="179" totalsRowDxfId="178"/>
-    <tableColumn id="1" name="Продукт" totalsRowLabel="Итог" dataDxfId="177" totalsRowDxfId="176"/>
-    <tableColumn id="12" name="Время приёма" dataDxfId="175" totalsRowDxfId="174"/>
-    <tableColumn id="9" name="Вес" totalsRowFunction="custom" dataDxfId="173" totalsRowDxfId="172">
+    <tableColumn id="11" name="Тип питания" dataDxfId="189" totalsRowDxfId="188"/>
+    <tableColumn id="1" name="Продукт" totalsRowLabel="Итог" dataDxfId="187" totalsRowDxfId="186"/>
+    <tableColumn id="12" name="Время приёма" dataDxfId="185" totalsRowDxfId="184"/>
+    <tableColumn id="9" name="Вес" totalsRowFunction="custom" dataDxfId="183" totalsRowDxfId="182">
       <totalsRowFormula>SUMPRODUCT(ПН[Вес], ПН[Количество])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="10" name="Количество" totalsRowFunction="sum" dataDxfId="171" totalsRowDxfId="170"/>
-    <tableColumn id="2" name="Исх. Вес." totalsRowFunction="sum" dataDxfId="169" totalsRowDxfId="168">
+    <tableColumn id="10" name="Количество" totalsRowFunction="sum" dataDxfId="181" totalsRowDxfId="180"/>
+    <tableColumn id="2" name="Исх. Вес." totalsRowFunction="sum" dataDxfId="179" totalsRowDxfId="178">
       <calculatedColumnFormula>INDEX(Продукты!$H:$H, MATCH(ПН[[#This Row],[Продукт]], Продукты!$A:$A, 0))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" name="Белки" totalsRowFunction="custom" dataDxfId="167" totalsRowDxfId="166">
+    <tableColumn id="3" name="Белки" totalsRowFunction="custom" dataDxfId="177" totalsRowDxfId="176">
       <calculatedColumnFormula>INDEX(Продукты!$B:$B, MATCH(ПН[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ПН[[#This Row],[Вес]]/ПН[Исх. Вес.])*ПН[Количество]</calculatedColumnFormula>
       <totalsRowFormula>SUMPRODUCT(ПН[Белки], ПН[Количество])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="4" name="Жиры" totalsRowFunction="custom" dataDxfId="165" totalsRowDxfId="164">
+    <tableColumn id="4" name="Жиры" totalsRowFunction="custom" dataDxfId="175" totalsRowDxfId="174">
       <calculatedColumnFormula>INDEX(Продукты!$C:$C, MATCH(ПН[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ПН[[#This Row],[Вес]]/ПН[Исх. Вес.])*ПН[Количество]</calculatedColumnFormula>
       <totalsRowFormula>SUMPRODUCT(ПН[Жиры], ПН[Количество])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" name="Углеводы" totalsRowFunction="custom" dataDxfId="163" totalsRowDxfId="162">
+    <tableColumn id="5" name="Углеводы" totalsRowFunction="custom" dataDxfId="173" totalsRowDxfId="172">
       <calculatedColumnFormula>INDEX(Продукты!$D:$D, MATCH(ПН[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ПН[[#This Row],[Вес]]/ПН[Исх. Вес.])*ПН[Количество]</calculatedColumnFormula>
       <totalsRowFormula>SUMPRODUCT(ПН[Углеводы], ПН[Количество])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="6" name="Клетчатка" totalsRowFunction="custom" dataDxfId="161" totalsRowDxfId="160">
+    <tableColumn id="6" name="Клетчатка" totalsRowFunction="custom" dataDxfId="171" totalsRowDxfId="170">
       <calculatedColumnFormula>INDEX(Продукты!$E:$E, MATCH(ПН[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ПН[[#This Row],[Вес]]/ПН[Исх. Вес.])*ПН[Количество]</calculatedColumnFormula>
       <totalsRowFormula>SUMPRODUCT(ПН[Клетчатка], ПН[Количество])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="7" name="Пищевые волокна" totalsRowFunction="custom" dataDxfId="159" totalsRowDxfId="158">
+    <tableColumn id="7" name="Пищевые волокна" totalsRowFunction="custom" dataDxfId="169" totalsRowDxfId="168">
       <calculatedColumnFormula>INDEX(Продукты!$F:$F, MATCH(ПН[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ПН[[#This Row],[Вес]]/ПН[Исх. Вес.])*ПН[Количество]</calculatedColumnFormula>
       <totalsRowFormula>SUMPRODUCT(ПН[Пищевые волокна], ПН[Количество])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="8" name="Калории, ккл" totalsRowFunction="sum" dataDxfId="157" totalsRowDxfId="156">
+    <tableColumn id="8" name="Калории, ккл" totalsRowFunction="sum" dataDxfId="167" totalsRowDxfId="166">
       <calculatedColumnFormula>INDEX(Продукты!$G:$G, MATCH(ПН[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ПН[[#This Row],[Вес]]/ПН[Исх. Вес.])*ПН[Количество]</calculatedColumnFormula>
-    </tableColumn>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="ВТ" displayName="ВТ" ref="A1:L2" headerRowDxfId="155" dataDxfId="154">
-  <autoFilter ref="A1:L2">
-    <filterColumn colId="0" hiddenButton="1"/>
-    <filterColumn colId="1" hiddenButton="1"/>
-    <filterColumn colId="2" hiddenButton="1"/>
-    <filterColumn colId="3" hiddenButton="1"/>
-    <filterColumn colId="4" hiddenButton="1"/>
-    <filterColumn colId="5" hiddenButton="1"/>
-    <filterColumn colId="6" hiddenButton="1"/>
-    <filterColumn colId="7" hiddenButton="1"/>
-    <filterColumn colId="8" hiddenButton="1"/>
-    <filterColumn colId="9" hiddenButton="1"/>
-    <filterColumn colId="10" hiddenButton="1"/>
-    <filterColumn colId="11" hiddenButton="1"/>
-  </autoFilter>
-  <tableColumns count="12">
-    <tableColumn id="11" name="Тип питания" dataDxfId="153" totalsRowDxfId="152"/>
-    <tableColumn id="1" name="Продукт" totalsRowLabel="Итог" dataDxfId="151" totalsRowDxfId="150"/>
-    <tableColumn id="12" name="Время приёма" dataDxfId="149" totalsRowDxfId="148"/>
-    <tableColumn id="9" name="Вес" totalsRowFunction="custom" dataDxfId="147" totalsRowDxfId="146">
-      <totalsRowFormula>SUMPRODUCT(ВТ[Вес], ВТ[Количество])</totalsRowFormula>
-    </tableColumn>
-    <tableColumn id="10" name="Количество" totalsRowFunction="sum" dataDxfId="145" totalsRowDxfId="144"/>
-    <tableColumn id="2" name="Исх. Вес." totalsRowFunction="sum" dataDxfId="143" totalsRowDxfId="142">
-      <calculatedColumnFormula>INDEX(Продукты!$H:$H, MATCH(ВТ[[#This Row],[Продукт]], Продукты!$A:$A, 0))</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="3" name="Белки" totalsRowFunction="custom" dataDxfId="141" totalsRowDxfId="140">
-      <calculatedColumnFormula>INDEX(Продукты!$B:$B, MATCH(ВТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ВТ[[#This Row],[Вес]]/ВТ[Исх. Вес.])*ВТ[Количество]</calculatedColumnFormula>
-      <totalsRowFormula>SUMPRODUCT(ВТ[Белки], ВТ[Количество])</totalsRowFormula>
-    </tableColumn>
-    <tableColumn id="4" name="Жиры" totalsRowFunction="custom" dataDxfId="139" totalsRowDxfId="138">
-      <calculatedColumnFormula>INDEX(Продукты!$C:$C, MATCH(ВТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ВТ[[#This Row],[Вес]]/ВТ[Исх. Вес.])*ВТ[Количество]</calculatedColumnFormula>
-      <totalsRowFormula>SUMPRODUCT(ВТ[Жиры], ВТ[Количество])</totalsRowFormula>
-    </tableColumn>
-    <tableColumn id="5" name="Углеводы" totalsRowFunction="custom" dataDxfId="137" totalsRowDxfId="136">
-      <calculatedColumnFormula>INDEX(Продукты!$D:$D, MATCH(ВТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ВТ[[#This Row],[Вес]]/ВТ[Исх. Вес.])*ВТ[Количество]</calculatedColumnFormula>
-      <totalsRowFormula>SUMPRODUCT(ВТ[Углеводы], ВТ[Количество])</totalsRowFormula>
-    </tableColumn>
-    <tableColumn id="6" name="Клетчатка" totalsRowFunction="custom" dataDxfId="135" totalsRowDxfId="134">
-      <calculatedColumnFormula>INDEX(Продукты!$E:$E, MATCH(ВТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ВТ[[#This Row],[Вес]]/ВТ[Исх. Вес.])*ВТ[Количество]</calculatedColumnFormula>
-      <totalsRowFormula>SUMPRODUCT(ВТ[Клетчатка], ВТ[Количество])</totalsRowFormula>
-    </tableColumn>
-    <tableColumn id="7" name="Пищевые волокна" totalsRowFunction="custom" dataDxfId="133" totalsRowDxfId="132">
-      <calculatedColumnFormula>INDEX(Продукты!$F:$F, MATCH(ВТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ВТ[[#This Row],[Вес]]/ВТ[Исх. Вес.])*ВТ[Количество]</calculatedColumnFormula>
-      <totalsRowFormula>SUMPRODUCT(ВТ[Пищевые волокна], ВТ[Количество])</totalsRowFormula>
-    </tableColumn>
-    <tableColumn id="8" name="Калории, ккл" totalsRowFunction="sum" dataDxfId="131" totalsRowDxfId="130">
-      <calculatedColumnFormula>INDEX(Продукты!$G:$G, MATCH(ВТ[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (ВТ[[#This Row],[Вес]]/ВТ[Исх. Вес.])*ВТ[Количество]</calculatedColumnFormula>
-    </tableColumn>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="СР" displayName="СР" ref="A1:L2" headerRowDxfId="129" dataDxfId="128">
-  <autoFilter ref="A1:L2">
-    <filterColumn colId="0" hiddenButton="1"/>
-    <filterColumn colId="1" hiddenButton="1"/>
-    <filterColumn colId="2" hiddenButton="1"/>
-    <filterColumn colId="3" hiddenButton="1"/>
-    <filterColumn colId="4" hiddenButton="1"/>
-    <filterColumn colId="5" hiddenButton="1"/>
-    <filterColumn colId="6" hiddenButton="1"/>
-    <filterColumn colId="7" hiddenButton="1"/>
-    <filterColumn colId="8" hiddenButton="1"/>
-    <filterColumn colId="9" hiddenButton="1"/>
-    <filterColumn colId="10" hiddenButton="1"/>
-    <filterColumn colId="11" hiddenButton="1"/>
-  </autoFilter>
-  <tableColumns count="12">
-    <tableColumn id="11" name="Тип питания" dataDxfId="127" totalsRowDxfId="126"/>
-    <tableColumn id="1" name="Продукт" totalsRowLabel="Итог" dataDxfId="125" totalsRowDxfId="124"/>
-    <tableColumn id="12" name="Время приёма" dataDxfId="123" totalsRowDxfId="122"/>
-    <tableColumn id="9" name="Вес" totalsRowFunction="custom" dataDxfId="121" totalsRowDxfId="120">
-      <totalsRowFormula>SUMPRODUCT(СР[Вес], СР[Количество])</totalsRowFormula>
-    </tableColumn>
-    <tableColumn id="10" name="Количество" totalsRowFunction="sum" dataDxfId="119" totalsRowDxfId="118"/>
-    <tableColumn id="2" name="Исх. Вес." totalsRowFunction="sum" dataDxfId="117" totalsRowDxfId="116">
-      <calculatedColumnFormula>INDEX(Продукты!$H:$H, MATCH(СР[[#This Row],[Продукт]], Продукты!$A:$A, 0))</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="3" name="Белки" totalsRowFunction="custom" dataDxfId="115" totalsRowDxfId="114">
-      <calculatedColumnFormula>INDEX(Продукты!$B:$B, MATCH(СР[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (СР[[#This Row],[Вес]]/СР[Исх. Вес.])*СР[Количество]</calculatedColumnFormula>
-      <totalsRowFormula>SUMPRODUCT(СР[Белки], СР[Количество])</totalsRowFormula>
-    </tableColumn>
-    <tableColumn id="4" name="Жиры" totalsRowFunction="custom" dataDxfId="113" totalsRowDxfId="112">
-      <calculatedColumnFormula>INDEX(Продукты!$C:$C, MATCH(СР[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (СР[[#This Row],[Вес]]/СР[Исх. Вес.])*СР[Количество]</calculatedColumnFormula>
-      <totalsRowFormula>SUMPRODUCT(СР[Жиры], СР[Количество])</totalsRowFormula>
-    </tableColumn>
-    <tableColumn id="5" name="Углеводы" totalsRowFunction="custom" dataDxfId="111" totalsRowDxfId="110">
-      <calculatedColumnFormula>INDEX(Продукты!$D:$D, MATCH(СР[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (СР[[#This Row],[Вес]]/СР[Исх. Вес.])*СР[Количество]</calculatedColumnFormula>
-      <totalsRowFormula>SUMPRODUCT(СР[Углеводы], СР[Количество])</totalsRowFormula>
-    </tableColumn>
-    <tableColumn id="6" name="Клетчатка" totalsRowFunction="custom" dataDxfId="109" totalsRowDxfId="108">
-      <calculatedColumnFormula>INDEX(Продукты!$E:$E, MATCH(СР[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (СР[[#This Row],[Вес]]/СР[Исх. Вес.])*СР[Количество]</calculatedColumnFormula>
-      <totalsRowFormula>SUMPRODUCT(СР[Клетчатка], СР[Количество])</totalsRowFormula>
-    </tableColumn>
-    <tableColumn id="7" name="Пищевые волокна" totalsRowFunction="custom" dataDxfId="107" totalsRowDxfId="106">
-      <calculatedColumnFormula>INDEX(Продукты!$F:$F, MATCH(СР[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (СР[[#This Row],[Вес]]/СР[Исх. Вес.])*СР[Количество]</calculatedColumnFormula>
-      <totalsRowFormula>SUMPRODUCT(СР[Пищевые волокна], СР[Количество])</totalsRowFormula>
-    </tableColumn>
-    <tableColumn id="8" name="Калории, ккл" totalsRowFunction="sum" dataDxfId="105" totalsRowDxfId="104">
-      <calculatedColumnFormula>INDEX(Продукты!$G:$G, MATCH(СР[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (СР[[#This Row],[Вес]]/СР[Исх. Вес.])*СР[Количество]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -11262,7 +11495,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:R2"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35.7109375" style="2" customWidth="1"/>
@@ -11274,10 +11507,14 @@
     <col min="8" max="8" width="13" style="1" customWidth="1"/>
     <col min="9" max="9" width="20.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="16" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="2"/>
+    <col min="11" max="12" width="9.140625" style="2"/>
+    <col min="13" max="13" width="12" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="9.140625" style="2"/>
+    <col min="17" max="17" width="12" style="2" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
@@ -11308,8 +11545,26 @@
       <c r="J1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L1" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="D2" s="1" t="e">
         <f>INDEX(Продукты!$H:$H, MATCH(Рассчет[[#This Row],[Продукт]], Продукты!$A:$A, 0))</f>
         <v>#N/A</v>
@@ -11336,6 +11591,25 @@
       </c>
       <c r="J2" s="1" t="e">
         <f>INDEX(Продукты!$G:$G, MATCH(Рассчет[[#This Row],[Продукт]], Продукты!$A:$A, 0)) * (Рассчет[[#This Row],[Вес, гр]]/Рассчет[Исх. Вес. гр])*Рассчет[Количество]</f>
+        <v>#N/A</v>
+      </c>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1" t="e">
+        <f>INDEX(Продукты!$I:$I, MATCH(Рассчет[Продукт], Продукты!$A:$A, 0))</f>
+        <v>#N/A</v>
+      </c>
+      <c r="N2" s="1" t="e">
+        <f>МлГр[Вес, мл.]*МлГр[Плотность]</f>
+        <v>#N/A</v>
+      </c>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1" t="e">
+        <f>INDEX(Продукты!$I:$I, MATCH(Рассчет[Продукт], Продукты!$A:$A, 0))</f>
+        <v>#N/A</v>
+      </c>
+      <c r="R2" s="1" t="e">
+        <f>ГрМл[Вес, гр]/ГрМл[Плотность]</f>
         <v>#N/A</v>
       </c>
     </row>
@@ -11347,8 +11621,10 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="86" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
-  <tableParts count="1">
+  <tableParts count="3">
     <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId4"/>
   </tableParts>
 </worksheet>
 </file>
